--- a/openalaqs_standalone/validation/data/training_validation_reference.xlsx
+++ b/openalaqs_standalone/validation/data/training_validation_reference.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Made on 2026-10-15 by openalaqs_standalone/validation/tools/regenerate_training_validation_xlsx.py</t>
+          <t>Made on 2026-10-19 by openalaqs_standalone/validation/tools/regenerate_training_validation_xlsx.py</t>
         </is>
       </c>
     </row>
@@ -1315,16 +1315,16 @@
         <v>21.81223996439635</v>
       </c>
       <c r="D3" t="n">
-        <v>22.48851076851739</v>
+        <v>22.48850242640301</v>
       </c>
       <c r="E3" t="n">
-        <v>22.4883801409646</v>
+        <v>22.48837179885023</v>
       </c>
       <c r="F3" t="n">
-        <v>21.53183425684955</v>
+        <v>21.53183246107695</v>
       </c>
       <c r="G3" t="n">
-        <v>21.53183425684935</v>
+        <v>21.53183246107675</v>
       </c>
       <c r="H3" t="n">
         <v>21.81223996439661</v>
@@ -1346,10 +1346,10 @@
         <v>6844.965817391669</v>
       </c>
       <c r="D4" t="n">
-        <v>5242.233985938513</v>
+        <v>5242.223667553793</v>
       </c>
       <c r="E4" t="n">
-        <v>5242.216365796728</v>
+        <v>5242.206047412008</v>
       </c>
       <c r="F4" t="n">
         <v>6850.849475311976</v>
@@ -1377,16 +1377,16 @@
         <v>1.456344821276915</v>
       </c>
       <c r="D5" t="n">
-        <v>1.468968495629321</v>
+        <v>1.468968287822269</v>
       </c>
       <c r="E5" t="n">
-        <v>1.46896674426592</v>
+        <v>1.468966536458868</v>
       </c>
       <c r="F5" t="n">
-        <v>1.46761813283704</v>
+        <v>1.467618076002955</v>
       </c>
       <c r="G5" t="n">
-        <v>1.467618132837034</v>
+        <v>1.467618076002949</v>
       </c>
       <c r="H5" t="n">
         <v>1.456344821276921</v>
@@ -1408,16 +1408,16 @@
         <v>29.1973548360385</v>
       </c>
       <c r="D6" t="n">
-        <v>15.27453935744864</v>
+        <v>15.27450936653538</v>
       </c>
       <c r="E6" t="n">
-        <v>15.27451834456961</v>
+        <v>15.27448835365636</v>
       </c>
       <c r="F6" t="n">
-        <v>27.745165198134</v>
+        <v>27.74544823479609</v>
       </c>
       <c r="G6" t="n">
-        <v>27.74516519813321</v>
+        <v>27.7454482347953</v>
       </c>
       <c r="H6" t="n">
         <v>27.96272566796094</v>
@@ -1470,10 +1470,10 @@
         <v>0.3056420782375103</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2723089391591127</v>
+        <v>0.2723087476335246</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2723086507953926</v>
+        <v>0.2723084592698045</v>
       </c>
       <c r="F8" t="n">
         <v>0.305953786407249</v>
@@ -1941,16 +1941,16 @@
         <v>1.249383207595792</v>
       </c>
       <c r="E4" t="n">
-        <v>1.337250601584687</v>
+        <v>1.337250514293041</v>
       </c>
       <c r="F4" t="n">
-        <v>1.337250601584647</v>
+        <v>1.337250514293001</v>
       </c>
       <c r="G4" t="n">
-        <v>1.284589733219643</v>
+        <v>1.284589582542515</v>
       </c>
       <c r="H4" t="n">
-        <v>1.284589733219615</v>
+        <v>1.284589582542488</v>
       </c>
       <c r="I4" t="n">
         <v>335.810093249882</v>
@@ -1959,10 +1959,10 @@
         <v>335.8100932498548</v>
       </c>
       <c r="K4" t="n">
-        <v>315.5750223723269</v>
+        <v>315.5749663487118</v>
       </c>
       <c r="L4" t="n">
-        <v>315.5750223723065</v>
+        <v>315.5749663486914</v>
       </c>
       <c r="M4" t="n">
         <v>346.5954463282931</v>
@@ -1977,16 +1977,16 @@
         <v>0.01699799872647318</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01831898619034413</v>
+        <v>0.01831898487119018</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01831898619034354</v>
+        <v>0.01831898487118959</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01747816384292438</v>
+        <v>0.01747816171805254</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01747816384292398</v>
+        <v>0.01747816171805214</v>
       </c>
       <c r="U4" t="n">
         <v>0.7187596353001016</v>
@@ -1995,16 +1995,16 @@
         <v>0.7187596353000264</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6236860383304756</v>
+        <v>0.6236859001187546</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6236860383304288</v>
+        <v>0.6236859001187076</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7536836115789314</v>
+        <v>0.7536837466262534</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.7536836115788557</v>
+        <v>0.7536837466261775</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -2031,10 +2031,10 @@
         <v>0.03448261318492375</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.03412611601861686</v>
+        <v>0.03412611505773455</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0341261160186165</v>
+        <v>0.0341261150577342</v>
       </c>
       <c r="AK4" t="n">
         <v>0.03465815909623058</v>
@@ -2059,10 +2059,10 @@
         <v>1.215414648670442</v>
       </c>
       <c r="E5" t="n">
-        <v>1.228964404756232</v>
+        <v>1.228964391559596</v>
       </c>
       <c r="F5" t="n">
-        <v>1.228964404756244</v>
+        <v>1.228964391559608</v>
       </c>
       <c r="G5" t="n">
         <v>1.231490660925481</v>
@@ -2077,10 +2077,10 @@
         <v>619.2711847860455</v>
       </c>
       <c r="K5" t="n">
-        <v>597.2314934155941</v>
+        <v>597.2313179543531</v>
       </c>
       <c r="L5" t="n">
-        <v>597.2314934157747</v>
+        <v>597.2313179545337</v>
       </c>
       <c r="M5" t="n">
         <v>630.8203587257171</v>
@@ -2095,10 +2095,10 @@
         <v>0.01866143787839269</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01854634816224502</v>
+        <v>0.01854634710651411</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0185463481622461</v>
+        <v>0.01854634710651518</v>
       </c>
       <c r="S5" t="n">
         <v>0.01874844865578491</v>
@@ -2113,16 +2113,16 @@
         <v>4.181440045730325</v>
       </c>
       <c r="W5" t="n">
-        <v>2.690133798904022</v>
+        <v>2.690133029617788</v>
       </c>
       <c r="X5" t="n">
-        <v>2.690133798905215</v>
+        <v>2.690133029618981</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.479758886197385</v>
+        <v>3.479763630920797</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.479758886198871</v>
+        <v>3.479763630922283</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -2149,10 +2149,10 @@
         <v>0.01025643025501781</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.009884811562013115</v>
+        <v>0.009884808647922837</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.009884811562016137</v>
+        <v>0.009884808647925861</v>
       </c>
       <c r="AK5" t="n">
         <v>0.01044440836285858</v>
@@ -2177,16 +2177,16 @@
         <v>2.297353639816358</v>
       </c>
       <c r="E6" t="n">
-        <v>2.342018293243936</v>
+        <v>2.342018207918635</v>
       </c>
       <c r="F6" t="n">
-        <v>2.342018293243934</v>
+        <v>2.342018207918633</v>
       </c>
       <c r="G6" t="n">
-        <v>2.362280007296219</v>
+        <v>2.36227977867535</v>
       </c>
       <c r="H6" t="n">
-        <v>2.362280007296158</v>
+        <v>2.362279778675288</v>
       </c>
       <c r="I6" t="n">
         <v>335.1276846846325</v>
@@ -2195,10 +2195,10 @@
         <v>335.1276846845912</v>
       </c>
       <c r="K6" t="n">
-        <v>352.2156637285203</v>
+        <v>352.2156007779217</v>
       </c>
       <c r="L6" t="n">
-        <v>352.2156637284581</v>
+        <v>352.2156007778595</v>
       </c>
       <c r="M6" t="n">
         <v>345.6226317182782</v>
@@ -2213,16 +2213,16 @@
         <v>0.2051001262108993</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2097966577282762</v>
+        <v>0.2097966550969538</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2097966577282752</v>
+        <v>0.2097966550969528</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2096115961436986</v>
+        <v>0.2096115860953342</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2096115961436968</v>
+        <v>0.2096115860953324</v>
       </c>
       <c r="U6" t="n">
         <v>0.6311932261730516</v>
@@ -2231,16 +2231,16 @@
         <v>0.6311932261729478</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6870579767542845</v>
+        <v>0.687057815017512</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6870579767540811</v>
+        <v>0.6870578150173086</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6542069679189838</v>
+        <v>0.6542070955549888</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6542069679188804</v>
+        <v>0.6542070955548853</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -2267,10 +2267,10 @@
         <v>0.02122330093920498</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0216057154920786</v>
+        <v>0.02160571434896728</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.02160571549207747</v>
+        <v>0.02160571434896615</v>
       </c>
       <c r="AK6" t="n">
         <v>0.0214859935243623</v>
@@ -2295,10 +2295,10 @@
         <v>2.345789062664461</v>
       </c>
       <c r="E7" t="n">
-        <v>2.326634881478983</v>
+        <v>2.326634843410283</v>
       </c>
       <c r="F7" t="n">
-        <v>2.326634881478983</v>
+        <v>2.326634843410283</v>
       </c>
       <c r="G7" t="n">
         <v>2.364219089796852</v>
@@ -2313,10 +2313,10 @@
         <v>684.900007607592</v>
       </c>
       <c r="K7" t="n">
-        <v>545.5515383251429</v>
+        <v>545.5513858679532</v>
       </c>
       <c r="L7" t="n">
-        <v>545.5515383251467</v>
+        <v>545.5513858679569</v>
       </c>
       <c r="M7" t="n">
         <v>696.0684395494593</v>
@@ -2331,10 +2331,10 @@
         <v>0.2216070221405273</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2230321114659466</v>
+        <v>0.2230321082553333</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2230321114659466</v>
+        <v>0.2230321082553333</v>
       </c>
       <c r="S7" t="n">
         <v>0.2262018639746825</v>
@@ -2349,16 +2349,16 @@
         <v>3.321360497065981</v>
       </c>
       <c r="W7" t="n">
-        <v>1.933417833204003</v>
+        <v>1.933417175668429</v>
       </c>
       <c r="X7" t="n">
-        <v>1.933417833204103</v>
+        <v>1.933417175668529</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.338618646680251</v>
+        <v>3.338619877406757</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.338618646680183</v>
+        <v>3.338619877406688</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0.0246764636409928</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.01900975608365247</v>
+        <v>0.01900975023441542</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01900975608365294</v>
+        <v>0.01900975023441589</v>
       </c>
       <c r="AK7" t="n">
         <v>0.02495601381399962</v>
@@ -2413,16 +2413,16 @@
         <v>1.249383207595792</v>
       </c>
       <c r="E8" t="n">
-        <v>1.330834682069931</v>
+        <v>1.330834349253787</v>
       </c>
       <c r="F8" t="n">
-        <v>1.330834682069891</v>
+        <v>1.330834349253747</v>
       </c>
       <c r="G8" t="n">
-        <v>1.275356580794605</v>
+        <v>1.275356016977138</v>
       </c>
       <c r="H8" t="n">
-        <v>1.275356580794578</v>
+        <v>1.275356016977111</v>
       </c>
       <c r="I8" t="n">
         <v>335.810093249882</v>
@@ -2431,10 +2431,10 @@
         <v>335.8100932498548</v>
       </c>
       <c r="K8" t="n">
-        <v>311.0623408520668</v>
+        <v>311.0621292957319</v>
       </c>
       <c r="L8" t="n">
-        <v>311.0623408520466</v>
+        <v>311.0621292957119</v>
       </c>
       <c r="M8" t="n">
         <v>344.1312513343726</v>
@@ -2449,16 +2449,16 @@
         <v>0.01699799872647318</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01823111862439451</v>
+        <v>0.01823111359486897</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01823111862439392</v>
+        <v>0.01823111359486838</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0173529769575071</v>
+        <v>0.01735296899159457</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01735297695750671</v>
+        <v>0.01735296899159417</v>
       </c>
       <c r="U8" t="n">
         <v>0.7187596353001016</v>
@@ -2467,16 +2467,16 @@
         <v>0.7187596353000264</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6194964295278248</v>
+        <v>0.6194959036029026</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6194964295277781</v>
+        <v>0.619495903602856</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.7606111743485361</v>
+        <v>0.7606117009603558</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.7606111743484587</v>
+        <v>0.7606117009602785</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -2503,10 +2503,10 @@
         <v>0.03448261318492375</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.03405087360943351</v>
+        <v>0.03405086998095042</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.03405087360943317</v>
+        <v>0.03405086998095008</v>
       </c>
       <c r="AK8" t="n">
         <v>0.03461805105779183</v>
@@ -2531,10 +2531,10 @@
         <v>1.215414648670439</v>
       </c>
       <c r="E9" t="n">
-        <v>1.223054946743832</v>
+        <v>1.223054896426163</v>
       </c>
       <c r="F9" t="n">
-        <v>1.22305494674383</v>
+        <v>1.223054896426162</v>
       </c>
       <c r="G9" t="n">
         <v>1.226052749055803</v>
@@ -2549,10 +2549,10 @@
         <v>619.2711847860041</v>
       </c>
       <c r="K9" t="n">
-        <v>588.7045815114777</v>
+        <v>588.7039188947367</v>
       </c>
       <c r="L9" t="n">
-        <v>588.7045815114722</v>
+        <v>588.703918894731</v>
       </c>
       <c r="M9" t="n">
         <v>628.1816489497982</v>
@@ -2567,10 +2567,10 @@
         <v>0.01866143787839243</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01845733545762789</v>
+        <v>0.0184573314322144</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01845733545762784</v>
+        <v>0.01845733143221435</v>
       </c>
       <c r="S9" t="n">
         <v>0.01869715964258556</v>
@@ -2585,16 +2585,16 @@
         <v>4.181440045729329</v>
       </c>
       <c r="W9" t="n">
-        <v>2.672096557523625</v>
+        <v>2.67209363004907</v>
       </c>
       <c r="X9" t="n">
-        <v>2.672096557523485</v>
+        <v>2.67209363004893</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.691728136781514</v>
+        <v>3.691747614455234</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.691728136781069</v>
+        <v>3.691747614454787</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -2621,10 +2621,10 @@
         <v>0.01025643025501708</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.009743684107073713</v>
+        <v>0.009743673102224338</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.009743684107073592</v>
+        <v>0.009743673102224211</v>
       </c>
       <c r="AK9" t="n">
         <v>0.01040145986512111</v>
@@ -2649,16 +2649,16 @@
         <v>2.297353639816358</v>
       </c>
       <c r="E10" t="n">
-        <v>2.330768473344632</v>
+        <v>2.330768148027796</v>
       </c>
       <c r="F10" t="n">
-        <v>2.330768473344631</v>
+        <v>2.330768148027794</v>
       </c>
       <c r="G10" t="n">
-        <v>2.345246361057552</v>
+        <v>2.34524550840041</v>
       </c>
       <c r="H10" t="n">
-        <v>2.345246361057492</v>
+        <v>2.345245508400351</v>
       </c>
       <c r="I10" t="n">
         <v>335.1276846846326</v>
@@ -2667,10 +2667,10 @@
         <v>335.1276846845912</v>
       </c>
       <c r="K10" t="n">
-        <v>347.1791073813126</v>
+        <v>347.1788696692248</v>
       </c>
       <c r="L10" t="n">
-        <v>347.1791073812512</v>
+        <v>347.1788696691634</v>
       </c>
       <c r="M10" t="n">
         <v>343.2247875537197</v>
@@ -2685,16 +2685,16 @@
         <v>0.2051001262108993</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2087879273037705</v>
+        <v>0.208787917271418</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2087879273037695</v>
+        <v>0.208787917271417</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2082971458646928</v>
+        <v>0.208297109169757</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2082971458646911</v>
+        <v>0.2082971091697554</v>
       </c>
       <c r="U10" t="n">
         <v>0.6311932261730516</v>
@@ -2703,16 +2703,16 @@
         <v>0.6311932261729478</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6824445135434923</v>
+        <v>0.6824438981058287</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6824445135432902</v>
+        <v>0.6824438981056268</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.6616338683925106</v>
+        <v>0.6616343670093586</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.661633868392405</v>
+        <v>0.6616343670092529</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -2739,10 +2739,10 @@
         <v>0.02122330093920498</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0214977805107234</v>
+        <v>0.02149777619414207</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.02149778051072229</v>
+        <v>0.02149777619414095</v>
       </c>
       <c r="AK10" t="n">
         <v>0.02142597455710395</v>
@@ -2767,10 +2767,10 @@
         <v>2.345789062664474</v>
       </c>
       <c r="E11" t="n">
-        <v>2.315449843888411</v>
+        <v>2.31544969873429</v>
       </c>
       <c r="F11" t="n">
-        <v>2.315449843888409</v>
+        <v>2.315449698734288</v>
       </c>
       <c r="G11" t="n">
         <v>2.354717979161599</v>
@@ -2785,10 +2785,10 @@
         <v>684.9000076076491</v>
       </c>
       <c r="K11" t="n">
-        <v>537.7609703247779</v>
+        <v>537.7603945757943</v>
       </c>
       <c r="L11" t="n">
-        <v>537.760970324774</v>
+        <v>537.7603945757903</v>
       </c>
       <c r="M11" t="n">
         <v>693.5167202055742</v>
@@ -2803,10 +2803,10 @@
         <v>0.2216070221405289</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2219598238758102</v>
+        <v>0.2219598116338963</v>
       </c>
       <c r="R11" t="n">
-        <v>0.22195982387581</v>
+        <v>0.2219598116338962</v>
       </c>
       <c r="S11" t="n">
         <v>0.2252715943205368</v>
@@ -2821,16 +2821,16 @@
         <v>3.321360497066278</v>
       </c>
       <c r="W11" t="n">
-        <v>1.920474722991172</v>
+        <v>1.920472220754318</v>
       </c>
       <c r="X11" t="n">
-        <v>1.920474722991095</v>
+        <v>1.920472220754241</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.40468122956453</v>
+        <v>3.404686044280208</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.404681229564597</v>
+        <v>3.404686044280275</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2857,10 +2857,10 @@
         <v>0.0246764636409948</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.01873839731773638</v>
+        <v>0.01873837522834602</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.01873839731773606</v>
+        <v>0.0187383752283457</v>
       </c>
       <c r="AK11" t="n">
         <v>0.02489214329146311</v>
@@ -2885,10 +2885,10 @@
         <v>1.249383207595792</v>
       </c>
       <c r="E12" t="n">
-        <v>1.303147068337098</v>
+        <v>1.3031447463793</v>
       </c>
       <c r="F12" t="n">
-        <v>1.303147068337058</v>
+        <v>1.30314474637926</v>
       </c>
       <c r="G12" t="n">
         <v>1.105027565371852</v>
@@ -2903,10 +2903,10 @@
         <v>335.8100932498548</v>
       </c>
       <c r="K12" t="n">
-        <v>269.9666515656853</v>
+        <v>269.9653435233846</v>
       </c>
       <c r="L12" t="n">
-        <v>269.9666515656678</v>
+        <v>269.9653435233672</v>
       </c>
       <c r="M12" t="n">
         <v>321.7213915807532</v>
@@ -2921,10 +2921,10 @@
         <v>0.01699799872647318</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.01785193455201139</v>
+        <v>0.01785189946258983</v>
       </c>
       <c r="R12" t="n">
-        <v>0.01785193455201081</v>
+        <v>0.01785189946258925</v>
       </c>
       <c r="S12" t="n">
         <v>0.01581220239032785</v>
@@ -2939,16 +2939,16 @@
         <v>0.7187596353000264</v>
       </c>
       <c r="W12" t="n">
-        <v>0.4104946108099706</v>
+        <v>0.4104921282085087</v>
       </c>
       <c r="X12" t="n">
-        <v>0.4104946108099397</v>
+        <v>0.4104921282084778</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.583595124967168</v>
+        <v>0.5835968813276599</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.5835951249671044</v>
+        <v>0.5835968813275964</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2975,10 +2975,10 @@
         <v>0.03448261318492375</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.03336563568812543</v>
+        <v>0.03336561325339493</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.03336563568812513</v>
+        <v>0.03336561325339464</v>
       </c>
       <c r="AK12" t="n">
         <v>0.03425330089856233</v>
@@ -3003,10 +3003,10 @@
         <v>1.215414648670426</v>
       </c>
       <c r="E13" t="n">
-        <v>1.197550512442898</v>
+        <v>1.197550161296834</v>
       </c>
       <c r="F13" t="n">
-        <v>1.197550512442885</v>
+        <v>1.197550161296821</v>
       </c>
       <c r="G13" t="n">
         <v>1.205536638909188</v>
@@ -3021,10 +3021,10 @@
         <v>619.2711847858455</v>
       </c>
       <c r="K13" t="n">
-        <v>510.9822751576089</v>
+        <v>510.9781770918903</v>
       </c>
       <c r="L13" t="n">
-        <v>510.9822751574757</v>
+        <v>510.9781770917572</v>
       </c>
       <c r="M13" t="n">
         <v>604.1847184477541</v>
@@ -3039,10 +3039,10 @@
         <v>0.01866143787839143</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01807319964116388</v>
+        <v>0.01807317154947878</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01807319964116295</v>
+        <v>0.01807317154947786</v>
       </c>
       <c r="S13" t="n">
         <v>0.01871208975846715</v>
@@ -3057,16 +3057,16 @@
         <v>4.181440045728492</v>
       </c>
       <c r="W13" t="n">
-        <v>1.77070464938974</v>
+        <v>1.770690826555561</v>
       </c>
       <c r="X13" t="n">
-        <v>1.77070464938904</v>
+        <v>1.770690826554862</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.540902671599877</v>
+        <v>3.540944914621419</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.540902671598635</v>
+        <v>3.540944914620177</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -3093,10 +3093,10 @@
         <v>0.01025643025501447</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.008457305411265527</v>
+        <v>0.00845723734998324</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.008457305411263299</v>
+        <v>0.008457237349981014</v>
       </c>
       <c r="AK13" t="n">
         <v>0.01001087802668609</v>
@@ -3181,10 +3181,10 @@
         <v>0.2649614504087965</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.633026679038728</v>
+        <v>5.633230032435653</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.633026679038726</v>
+        <v>5.633230032435653</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -3239,10 +3239,10 @@
         <v>2.297353639816358</v>
       </c>
       <c r="E15" t="n">
-        <v>2.282217923540017</v>
+        <v>2.282215653974355</v>
       </c>
       <c r="F15" t="n">
-        <v>2.282217923540016</v>
+        <v>2.282215653974355</v>
       </c>
       <c r="G15" t="n">
         <v>2.097121851084944</v>
@@ -3257,10 +3257,10 @@
         <v>335.1276846845912</v>
       </c>
       <c r="K15" t="n">
-        <v>301.3122134169184</v>
+        <v>301.3107437093103</v>
       </c>
       <c r="L15" t="n">
-        <v>301.3122134168652</v>
+        <v>301.3107437092571</v>
       </c>
       <c r="M15" t="n">
         <v>321.4183349104175</v>
@@ -3275,10 +3275,10 @@
         <v>0.2051001262108993</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2044343943811958</v>
+        <v>0.204434324390698</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2044343943811948</v>
+        <v>0.2044343243906969</v>
       </c>
       <c r="S15" t="n">
         <v>0.201414625622615</v>
@@ -3293,16 +3293,16 @@
         <v>0.6311932261729478</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4522113124136231</v>
+        <v>0.4522084073817672</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4522113124134892</v>
+        <v>0.4522084073816333</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5222792361394833</v>
+        <v>0.5222816079108108</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.522279236139394</v>
+        <v>0.5222816079107214</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -3329,10 +3329,10 @@
         <v>0.02122330093920498</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.02051504629581665</v>
+        <v>0.02051501960759695</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.02051504629581569</v>
+        <v>0.02051501960759598</v>
       </c>
       <c r="AK15" t="n">
         <v>0.02088015060967489</v>
@@ -3357,10 +3357,10 @@
         <v>1.249383207595792</v>
       </c>
       <c r="E16" t="n">
-        <v>1.303147068337098</v>
+        <v>1.3031447463793</v>
       </c>
       <c r="F16" t="n">
-        <v>1.303147068337058</v>
+        <v>1.30314474637926</v>
       </c>
       <c r="G16" t="n">
         <v>1.105027565371852</v>
@@ -3375,10 +3375,10 @@
         <v>335.8100932498548</v>
       </c>
       <c r="K16" t="n">
-        <v>269.9666515656853</v>
+        <v>269.9653435233847</v>
       </c>
       <c r="L16" t="n">
-        <v>269.9666515656678</v>
+        <v>269.9653435233672</v>
       </c>
       <c r="M16" t="n">
         <v>321.7213915807532</v>
@@ -3393,10 +3393,10 @@
         <v>0.01699799872647318</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01785193455201139</v>
+        <v>0.01785189946258983</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01785193455201081</v>
+        <v>0.01785189946258925</v>
       </c>
       <c r="S16" t="n">
         <v>0.01581220239032785</v>
@@ -3411,16 +3411,16 @@
         <v>0.7187596353000264</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4104946108099706</v>
+        <v>0.4104921282085087</v>
       </c>
       <c r="X16" t="n">
-        <v>0.4104946108099397</v>
+        <v>0.4104921282084778</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5835951249671679</v>
+        <v>0.5835968813276599</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.5835951249671044</v>
+        <v>0.5835968813275964</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -3447,10 +3447,10 @@
         <v>0.03448261318492375</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.03336563568812542</v>
+        <v>0.03336561325339493</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.03336563568812513</v>
+        <v>0.03336561325339464</v>
       </c>
       <c r="AK16" t="n">
         <v>0.03425330089856232</v>
@@ -3709,16 +3709,16 @@
         <v>21.81223996439635</v>
       </c>
       <c r="E19" t="n">
-        <v>22.48851076851739</v>
+        <v>22.48850242640301</v>
       </c>
       <c r="F19" t="n">
-        <v>22.4883801409646</v>
+        <v>22.48837179885023</v>
       </c>
       <c r="G19" t="n">
-        <v>21.53183425684955</v>
+        <v>21.53183246107695</v>
       </c>
       <c r="H19" t="n">
-        <v>21.53183425684935</v>
+        <v>21.53183246107675</v>
       </c>
       <c r="I19" t="n">
         <v>6844.96581739191</v>
@@ -3727,10 +3727,10 @@
         <v>6844.965817391669</v>
       </c>
       <c r="K19" t="n">
-        <v>5242.233985938513</v>
+        <v>5242.223667553793</v>
       </c>
       <c r="L19" t="n">
-        <v>5242.216365796728</v>
+        <v>5242.206047412008</v>
       </c>
       <c r="M19" t="n">
         <v>6850.849475311976</v>
@@ -3745,16 +3745,16 @@
         <v>1.456344821276915</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.468968495629321</v>
+        <v>1.468968287822269</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46896674426592</v>
+        <v>1.468966536458868</v>
       </c>
       <c r="S19" t="n">
-        <v>1.46761813283704</v>
+        <v>1.467618076002955</v>
       </c>
       <c r="T19" t="n">
-        <v>1.467618132837034</v>
+        <v>1.467618076002949</v>
       </c>
       <c r="U19" t="n">
         <v>29.19735483603938</v>
@@ -3763,16 +3763,16 @@
         <v>29.1973548360385</v>
       </c>
       <c r="W19" t="n">
-        <v>15.27453935744864</v>
+        <v>15.27450936653538</v>
       </c>
       <c r="X19" t="n">
-        <v>15.27451834456961</v>
+        <v>15.27448835365636</v>
       </c>
       <c r="Y19" t="n">
-        <v>27.745165198134</v>
+        <v>27.74544823479609</v>
       </c>
       <c r="Z19" t="n">
-        <v>27.74516519813321</v>
+        <v>27.7454482347953</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3799,10 +3799,10 @@
         <v>0.3056420782375103</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.2723089391591127</v>
+        <v>0.2723087476335246</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.2723086507953926</v>
+        <v>0.2723084592698045</v>
       </c>
       <c r="AK19" t="n">
         <v>0.305953786407249</v>
@@ -4444,16 +4444,16 @@
         <v>4.965394307439615</v>
       </c>
       <c r="C4" t="n">
-        <v>5.111476110941817</v>
+        <v>5.111475925128234</v>
       </c>
       <c r="D4" t="n">
-        <v>5.081603212798305</v>
+        <v>5.081602833500307</v>
       </c>
       <c r="E4" t="n">
         <v>1332.14616699492</v>
       </c>
       <c r="F4" t="n">
-        <v>1306.959383790995</v>
+        <v>1306.95908935554</v>
       </c>
       <c r="G4" t="n">
         <v>1364.975641046842</v>
@@ -4462,19 +4462,19 @@
         <v>0.3996213971670751</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4055238264321749</v>
+        <v>0.4055238214259677</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4047000429937173</v>
+        <v>0.4047000308204811</v>
       </c>
       <c r="K4" t="n">
         <v>5.615955500928096</v>
       </c>
       <c r="L4" t="n">
-        <v>4.085440407715285</v>
+        <v>4.085439338480557</v>
       </c>
       <c r="M4" t="n">
-        <v>4.972212059421802</v>
+        <v>4.972217066828541</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0.0686047346000699</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06825903329363395</v>
+        <v>0.06825902827555004</v>
       </c>
       <c r="S4" t="n">
         <v>0.06923095120437682</v>
@@ -4505,7 +4505,7 @@
         <v>2.462742325238724</v>
       </c>
       <c r="C5" t="n">
-        <v>2.443588144053244</v>
+        <v>2.443588105984543</v>
       </c>
       <c r="D5" t="n">
         <v>2.481172352371113</v>
@@ -4514,7 +4514,7 @@
         <v>715.4898562671651</v>
       </c>
       <c r="F5" t="n">
-        <v>576.1413869846958</v>
+        <v>576.1412345275061</v>
       </c>
       <c r="G5" t="n">
         <v>726.6582882090122</v>
@@ -4523,7 +4523,7 @@
         <v>0.3142863803465565</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3157114696719746</v>
+        <v>0.3157114664613613</v>
       </c>
       <c r="J5" t="n">
         <v>0.3188812221807105</v>
@@ -4532,10 +4532,10 @@
         <v>3.37364174329846</v>
       </c>
       <c r="L5" t="n">
-        <v>1.985699079436435</v>
+        <v>1.985698421900861</v>
       </c>
       <c r="M5" t="n">
-        <v>3.390899892912683</v>
+        <v>3.390901123639189</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
         <v>0.02635755366970532</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02069084611236461</v>
+        <v>0.02069084026312756</v>
       </c>
       <c r="S5" t="n">
         <v>0.02663710384271176</v>
@@ -4566,16 +4566,16 @@
         <v>2.464797856266255</v>
       </c>
       <c r="C6" t="n">
-        <v>2.553889628813764</v>
+        <v>2.553889245679951</v>
       </c>
       <c r="D6" t="n">
-        <v>2.501409329850407</v>
+        <v>2.50140876603294</v>
       </c>
       <c r="E6" t="n">
         <v>955.0812780359004</v>
       </c>
       <c r="F6" t="n">
-        <v>899.7669223635445</v>
+        <v>899.7660481904686</v>
       </c>
       <c r="G6" t="n">
         <v>972.3129002841708</v>
@@ -4584,19 +4584,19 @@
         <v>0.03565943660486603</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0366884540820224</v>
+        <v>0.03668844502708337</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03605013660009267</v>
+        <v>0.03605012863418014</v>
       </c>
       <c r="K6" t="n">
         <v>4.900199681030034</v>
       </c>
       <c r="L6" t="n">
-        <v>3.29159298705145</v>
+        <v>3.291589533651972</v>
       </c>
       <c r="M6" t="n">
-        <v>4.452339311130051</v>
+        <v>4.452359315415589</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -4611,7 +4611,7 @@
         <v>0.04473904343994156</v>
       </c>
       <c r="R6" t="n">
-        <v>0.04379455771650722</v>
+        <v>0.04379454308317475</v>
       </c>
       <c r="S6" t="n">
         <v>0.04501951092291294</v>
@@ -4627,16 +4627,16 @@
         <v>4.643142702480883</v>
       </c>
       <c r="C7" t="n">
-        <v>4.646218317233043</v>
+        <v>4.646217846762086</v>
       </c>
       <c r="D7" t="n">
-        <v>4.699964340219151</v>
+        <v>4.699963487562009</v>
       </c>
       <c r="E7" t="n">
         <v>1020.027692292266</v>
       </c>
       <c r="F7" t="n">
-        <v>884.9400777060905</v>
+        <v>884.9392642450191</v>
       </c>
       <c r="G7" t="n">
         <v>1036.741507759294</v>
@@ -4645,19 +4645,19 @@
         <v>0.4267071483514289</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4307477511795808</v>
+        <v>0.4307477289053144</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4335687401852297</v>
+        <v>0.4335687034902939</v>
       </c>
       <c r="K7" t="n">
         <v>3.952553723239276</v>
       </c>
       <c r="L7" t="n">
-        <v>2.602919236534664</v>
+        <v>2.602916118860147</v>
       </c>
       <c r="M7" t="n">
-        <v>4.066315097957041</v>
+        <v>4.066320411289567</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -4672,7 +4672,7 @@
         <v>0.04589976458020013</v>
       </c>
       <c r="R7" t="n">
-        <v>0.04023617782845978</v>
+        <v>0.04023615142248808</v>
       </c>
       <c r="S7" t="n">
         <v>0.04631811784856706</v>
@@ -4688,7 +4688,7 @@
         <v>2.464797856266254</v>
       </c>
       <c r="C8" t="n">
-        <v>2.500697580779995</v>
+        <v>2.500694907676134</v>
       </c>
       <c r="D8" t="n">
         <v>2.31056420428104</v>
@@ -4697,7 +4697,7 @@
         <v>955.08127803589</v>
       </c>
       <c r="F8" t="n">
-        <v>780.9489267232941</v>
+        <v>780.9435206152749</v>
       </c>
       <c r="G8" t="n">
         <v>925.9061100285073</v>
@@ -4706,7 +4706,7 @@
         <v>0.03565943660486598</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03592513419317527</v>
+        <v>0.03592507101206861</v>
       </c>
       <c r="J8" t="n">
         <v>0.034524292148795</v>
@@ -4715,10 +4715,10 @@
         <v>4.900199681030069</v>
       </c>
       <c r="L8" t="n">
-        <v>2.181199260199711</v>
+        <v>2.18118295476407</v>
       </c>
       <c r="M8" t="n">
-        <v>4.124497796567045</v>
+        <v>4.124541795949079</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -4733,7 +4733,7 @@
         <v>0.04473904343994139</v>
       </c>
       <c r="R8" t="n">
-        <v>0.04182294109939096</v>
+        <v>0.04182285060337818</v>
       </c>
       <c r="S8" t="n">
         <v>0.04426417892524841</v>
@@ -4749,7 +4749,7 @@
         <v>4.811364916704877</v>
       </c>
       <c r="C9" t="n">
-        <v>5.232640986695523</v>
+        <v>5.232636395172063</v>
       </c>
       <c r="D9" t="n">
         <v>4.457120817329539</v>
@@ -4758,7 +4758,7 @@
         <v>1867.139545765768</v>
       </c>
       <c r="F9" t="n">
-        <v>793.4772883698931</v>
+        <v>793.4745106199844</v>
       </c>
       <c r="G9" t="n">
         <v>1824.25502798415</v>
@@ -4767,7 +4767,7 @@
         <v>0.244411022202129</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2443718600703935</v>
+        <v>0.2443717549904741</v>
       </c>
       <c r="J9" t="n">
         <v>0.2398936987284944</v>
@@ -4776,10 +4776,10 @@
         <v>6.454804506513449</v>
       </c>
       <c r="L9" t="n">
-        <v>1.12768838651109</v>
+        <v>1.127682998877772</v>
       </c>
       <c r="M9" t="n">
-        <v>6.738901040145379</v>
+        <v>6.739108521674124</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
         <v>0.07530193850765612</v>
       </c>
       <c r="R9" t="n">
-        <v>0.05750538310875621</v>
+        <v>0.05750533398580601</v>
       </c>
       <c r="S9" t="n">
         <v>0.07448392366343196</v>

--- a/openalaqs_standalone/validation/data/training_validation_reference.xlsx
+++ b/openalaqs_standalone/validation/data/training_validation_reference.xlsx
@@ -490,7 +490,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Worst relative gap plugin vs reference: 4.5e-13 on the ANP and helicopter movements, 8.0e-05 on movement 11 (CUSTOM profile, supplied track).</t>
+          <t>Worst relative gap plugin vs reference: 3.0e-13 on the ANP and helicopter movements, 8.0e-05 on movement 11 (CUSTOM profile, supplied track).</t>
         </is>
       </c>
     </row>
@@ -1309,28 +1309,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.81223996439661</v>
+        <v>21.81223996439659</v>
       </c>
       <c r="C3" t="n">
-        <v>21.81223996439635</v>
+        <v>21.81223996439638</v>
       </c>
       <c r="D3" t="n">
-        <v>22.48850242640301</v>
+        <v>22.488502426403</v>
       </c>
       <c r="E3" t="n">
-        <v>22.48837179885023</v>
+        <v>22.48837179885026</v>
       </c>
       <c r="F3" t="n">
-        <v>21.53183246107695</v>
+        <v>21.53183246107693</v>
       </c>
       <c r="G3" t="n">
-        <v>21.53183246107675</v>
+        <v>21.53183246107677</v>
       </c>
       <c r="H3" t="n">
-        <v>21.81223996439661</v>
+        <v>21.81223996439659</v>
       </c>
       <c r="I3" t="n">
-        <v>21.81223996439635</v>
+        <v>21.81223996439638</v>
       </c>
     </row>
     <row r="4">
@@ -1340,28 +1340,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6844.96581739191</v>
+        <v>6844.965817391977</v>
       </c>
       <c r="C4" t="n">
-        <v>6844.965817391669</v>
+        <v>6844.965817391885</v>
       </c>
       <c r="D4" t="n">
-        <v>5242.223667553793</v>
+        <v>5242.223667553916</v>
       </c>
       <c r="E4" t="n">
-        <v>5242.206047412008</v>
+        <v>5242.206047412269</v>
       </c>
       <c r="F4" t="n">
-        <v>6850.849475311976</v>
+        <v>6850.849475312064</v>
       </c>
       <c r="G4" t="n">
-        <v>6850.849475311753</v>
+        <v>6850.84947531197</v>
       </c>
       <c r="H4" t="n">
-        <v>6844.96581739191</v>
+        <v>6844.965817391977</v>
       </c>
       <c r="I4" t="n">
-        <v>6844.965817391669</v>
+        <v>6844.965817391885</v>
       </c>
     </row>
     <row r="5">
@@ -1371,28 +1371,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.456344821276921</v>
+        <v>1.45634482127692</v>
       </c>
       <c r="C5" t="n">
-        <v>1.456344821276915</v>
+        <v>1.456344821276916</v>
       </c>
       <c r="D5" t="n">
         <v>1.468968287822269</v>
       </c>
       <c r="E5" t="n">
-        <v>1.468966536458868</v>
+        <v>1.46896653645887</v>
       </c>
       <c r="F5" t="n">
-        <v>1.467618076002955</v>
+        <v>1.467618076002954</v>
       </c>
       <c r="G5" t="n">
-        <v>1.467618076002949</v>
+        <v>1.467618076002951</v>
       </c>
       <c r="H5" t="n">
-        <v>1.456344821276921</v>
+        <v>1.45634482127692</v>
       </c>
       <c r="I5" t="n">
-        <v>1.456344821276915</v>
+        <v>1.456344821276916</v>
       </c>
     </row>
     <row r="6">
@@ -1402,28 +1402,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.19735483603938</v>
+        <v>29.19735483604114</v>
       </c>
       <c r="C6" t="n">
-        <v>29.1973548360385</v>
+        <v>29.19735483604121</v>
       </c>
       <c r="D6" t="n">
-        <v>15.27450936653538</v>
+        <v>15.2745093665372</v>
       </c>
       <c r="E6" t="n">
-        <v>15.27448835365636</v>
+        <v>15.27448835365928</v>
       </c>
       <c r="F6" t="n">
-        <v>27.74544823479609</v>
+        <v>27.74544823479723</v>
       </c>
       <c r="G6" t="n">
-        <v>27.7454482347953</v>
+        <v>27.74544823479732</v>
       </c>
       <c r="H6" t="n">
-        <v>27.96272566796094</v>
+        <v>27.96272566796256</v>
       </c>
       <c r="I6" t="n">
-        <v>27.96268670751492</v>
+        <v>27.96268670751743</v>
       </c>
     </row>
     <row r="7">
@@ -1433,28 +1433,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2.875232223852346</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.875232223852308</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2.201999369419103</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2.201991968067452</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2.877703658085513</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2.877703658085473</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2.875232223852346</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2.875232223852308</v>
       </c>
     </row>
     <row r="8">
@@ -1464,28 +1464,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3056420782375144</v>
+        <v>0.3056420782375127</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3056420782375103</v>
+        <v>0.3056420782375154</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2723087476335246</v>
+        <v>0.2723087476335245</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2723084592698045</v>
+        <v>0.2723084592698104</v>
       </c>
       <c r="F8" t="n">
-        <v>0.305953786407249</v>
+        <v>0.3059537864072475</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3059537864072451</v>
+        <v>0.3059537864072503</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3056420782375144</v>
+        <v>0.3056420782375127</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3056420782375103</v>
+        <v>0.3056420782375154</v>
       </c>
     </row>
   </sheetData>
@@ -2007,22 +2007,22 @@
         <v>0.7536837466261775</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>0.1410572422076466</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>0.1410572422076352</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>0.1325574643457678</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>0.1325574643457592</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>0.1455876365944061</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>0.1455876365943946</v>
       </c>
       <c r="AG4" t="n">
         <v>0.03448261318492422</v>
@@ -2053,112 +2053,112 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.215414648670428</v>
+        <v>1.215414648670441</v>
       </c>
       <c r="D5" t="n">
-        <v>1.215414648670442</v>
+        <v>1.21541464867044</v>
       </c>
       <c r="E5" t="n">
-        <v>1.228964391559596</v>
+        <v>1.22896439155961</v>
       </c>
       <c r="F5" t="n">
-        <v>1.228964391559608</v>
+        <v>1.22896439155961</v>
       </c>
       <c r="G5" t="n">
-        <v>1.231490660925481</v>
+        <v>1.231490660925495</v>
       </c>
       <c r="H5" t="n">
-        <v>1.231490660925494</v>
+        <v>1.231490660925493</v>
       </c>
       <c r="I5" t="n">
-        <v>619.2711847858524</v>
+        <v>619.2711847860421</v>
       </c>
       <c r="J5" t="n">
-        <v>619.2711847860455</v>
+        <v>619.2711847860321</v>
       </c>
       <c r="K5" t="n">
-        <v>597.2313179543531</v>
+        <v>597.2313179545397</v>
       </c>
       <c r="L5" t="n">
-        <v>597.2313179545337</v>
+        <v>597.2313179545572</v>
       </c>
       <c r="M5" t="n">
-        <v>630.8203587257171</v>
+        <v>630.8203587259069</v>
       </c>
       <c r="N5" t="n">
-        <v>630.82035872591</v>
+        <v>630.8203587258967</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01866143787839147</v>
+        <v>0.01866143787839267</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01866143787839269</v>
+        <v>0.01866143787839261</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01854634710651411</v>
+        <v>0.01854634710651523</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01854634710651518</v>
+        <v>0.01854634710651532</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01874844865578491</v>
+        <v>0.01874844865578606</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01874844865578607</v>
+        <v>0.01874844865578599</v>
       </c>
       <c r="U5" t="n">
-        <v>4.18144004572844</v>
+        <v>4.181440045730522</v>
       </c>
       <c r="V5" t="n">
-        <v>4.181440045730325</v>
+        <v>4.181440045730588</v>
       </c>
       <c r="W5" t="n">
-        <v>2.690133029617788</v>
+        <v>2.690133029619446</v>
       </c>
       <c r="X5" t="n">
-        <v>2.690133029618981</v>
+        <v>2.690133029619915</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.479763630920797</v>
+        <v>3.479763630922355</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.479763630922283</v>
+        <v>3.479763630922331</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>0.2601252531131649</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>0.2601252531131606</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>0.2508673931013095</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>0.2508673931013168</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>0.2649764909362088</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.2649764909362045</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.01025643025501458</v>
+        <v>0.01025643025501777</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.01025643025501781</v>
+        <v>0.01025643025501761</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.009884808647922837</v>
+        <v>0.009884808647925979</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.009884808647925861</v>
+        <v>0.009884808647926275</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.01044440836285858</v>
+        <v>0.01044440836286177</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01044440836286181</v>
+        <v>0.01044440836286161</v>
       </c>
     </row>
     <row r="6">
@@ -2177,7 +2177,7 @@
         <v>2.297353639816358</v>
       </c>
       <c r="E6" t="n">
-        <v>2.342018207918635</v>
+        <v>2.342018207918636</v>
       </c>
       <c r="F6" t="n">
         <v>2.342018207918633</v>
@@ -2189,7 +2189,7 @@
         <v>2.362279778675288</v>
       </c>
       <c r="I6" t="n">
-        <v>335.1276846846325</v>
+        <v>335.1276846846326</v>
       </c>
       <c r="J6" t="n">
         <v>335.1276846845912</v>
@@ -2213,7 +2213,7 @@
         <v>0.2051001262108993</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2097966550969538</v>
+        <v>0.2097966550969539</v>
       </c>
       <c r="R6" t="n">
         <v>0.2097966550969528</v>
@@ -2231,34 +2231,34 @@
         <v>0.6311932261729478</v>
       </c>
       <c r="W6" t="n">
-        <v>0.687057815017512</v>
+        <v>0.6870578150175121</v>
       </c>
       <c r="X6" t="n">
         <v>0.6870578150173086</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6542070955549888</v>
+        <v>0.654207095554989</v>
       </c>
       <c r="Z6" t="n">
         <v>0.6542070955548853</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>0.1407705960579095</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>0.1407705960578921</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>0.1479483860280324</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>0.1479483860280062</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>0.1451790052017638</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.1451790052017465</v>
       </c>
       <c r="AG6" t="n">
         <v>0.02122330093920573</v>
@@ -2267,7 +2267,7 @@
         <v>0.02122330093920498</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.02160571434896728</v>
+        <v>0.02160571434896729</v>
       </c>
       <c r="AJ6" t="n">
         <v>0.02160571434896615</v>
@@ -2289,112 +2289,112 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.345789062664463</v>
+        <v>2.34578906266445</v>
       </c>
       <c r="D7" t="n">
-        <v>2.345789062664461</v>
+        <v>2.345789062664475</v>
       </c>
       <c r="E7" t="n">
-        <v>2.326634843410283</v>
+        <v>2.326634843410275</v>
       </c>
       <c r="F7" t="n">
-        <v>2.326634843410283</v>
+        <v>2.326634843410293</v>
       </c>
       <c r="G7" t="n">
-        <v>2.364219089796852</v>
+        <v>2.364219089796838</v>
       </c>
       <c r="H7" t="n">
-        <v>2.364219089796847</v>
+        <v>2.364219089796859</v>
       </c>
       <c r="I7" t="n">
-        <v>684.9000076076122</v>
+        <v>684.9000076075548</v>
       </c>
       <c r="J7" t="n">
-        <v>684.900007607592</v>
+        <v>684.9000076076422</v>
       </c>
       <c r="K7" t="n">
-        <v>545.5513858679532</v>
+        <v>545.5513858679183</v>
       </c>
       <c r="L7" t="n">
-        <v>545.5513858679569</v>
+        <v>545.5513858679952</v>
       </c>
       <c r="M7" t="n">
-        <v>696.0684395494593</v>
+        <v>696.0684395494019</v>
       </c>
       <c r="N7" t="n">
-        <v>696.0684395494389</v>
+        <v>696.0684395494893</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2216070221405285</v>
+        <v>0.221607022140527</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2216070221405273</v>
+        <v>0.221607022140528</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2230321082553333</v>
+        <v>0.2230321082553326</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2230321082553333</v>
+        <v>0.2230321082553341</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2262018639746825</v>
+        <v>0.2262018639746813</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2262018639746821</v>
+        <v>0.2262018639746831</v>
       </c>
       <c r="U7" t="n">
-        <v>3.321360497066028</v>
+        <v>3.321360497065732</v>
       </c>
       <c r="V7" t="n">
-        <v>3.321360497065981</v>
+        <v>3.321360497066309</v>
       </c>
       <c r="W7" t="n">
-        <v>1.933417175668429</v>
+        <v>1.933417175668302</v>
       </c>
       <c r="X7" t="n">
-        <v>1.933417175668529</v>
+        <v>1.933417175668724</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.338619877406757</v>
+        <v>3.33861987740645</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.338619877406688</v>
+        <v>3.338619877407011</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>0.2876926816765709</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>0.2876926816766076</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>0.2291592049195063</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>0.2291592049195386</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>0.2923839885823716</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>0.2923839885824082</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.02467646364099318</v>
+        <v>0.0246764636409912</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0246764636409928</v>
+        <v>0.02467646364099493</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.01900975023441542</v>
+        <v>0.01900975023441424</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01900975023441589</v>
+        <v>0.0190097502344175</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.02495601381399962</v>
+        <v>0.02495601381399763</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02495601381399923</v>
+        <v>0.02495601381400136</v>
       </c>
     </row>
     <row r="8">
@@ -2413,7 +2413,7 @@
         <v>1.249383207595792</v>
       </c>
       <c r="E8" t="n">
-        <v>1.330834349253787</v>
+        <v>1.330834349253788</v>
       </c>
       <c r="F8" t="n">
         <v>1.330834349253747</v>
@@ -2473,28 +2473,28 @@
         <v>0.619495903602856</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.7606117009603558</v>
+        <v>0.7606117009603559</v>
       </c>
       <c r="Z8" t="n">
         <v>0.7606117009602785</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>0.1410572422076466</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>0.1410572422076352</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>0.1306618442854375</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>0.1306618442854291</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>0.1445525499275927</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.1445525499275812</v>
       </c>
       <c r="AG8" t="n">
         <v>0.03448261318492422</v>
@@ -2509,7 +2509,7 @@
         <v>0.03405086998095008</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.03461805105779183</v>
+        <v>0.03461805105779184</v>
       </c>
       <c r="AL8" t="n">
         <v>0.03461805105779137</v>
@@ -2597,25 +2597,25 @@
         <v>3.691747614454787</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>0.2601252531131549</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>0.2601252531131489</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>0.2472854537291511</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>0.2472854537291488</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>0.2638680992246848</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>0.2638680992246788</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.01025643025501735</v>
+        <v>0.01025643025501734</v>
       </c>
       <c r="AH9" t="n">
         <v>0.01025643025501708</v>
@@ -2715,22 +2715,22 @@
         <v>0.6616343670092529</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>0.1407705960579095</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>0.1407705960578921</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>0.1458327039380197</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>0.1458327039379939</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>0.1441717892428182</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>0.1441717892428007</v>
       </c>
       <c r="AG10" t="n">
         <v>0.02122330093920573</v>
@@ -2761,112 +2761,112 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.345789062664472</v>
+        <v>2.34578906266445</v>
       </c>
       <c r="D11" t="n">
-        <v>2.345789062664474</v>
+        <v>2.345789062664475</v>
       </c>
       <c r="E11" t="n">
+        <v>2.315449698734272</v>
+      </c>
+      <c r="F11" t="n">
         <v>2.31544969873429</v>
       </c>
-      <c r="F11" t="n">
-        <v>2.315449698734288</v>
-      </c>
       <c r="G11" t="n">
-        <v>2.354717979161599</v>
+        <v>2.354717979161579</v>
       </c>
       <c r="H11" t="n">
-        <v>2.354717979161602</v>
+        <v>2.3547179791616</v>
       </c>
       <c r="I11" t="n">
-        <v>684.9000076076335</v>
+        <v>684.9000076075548</v>
       </c>
       <c r="J11" t="n">
-        <v>684.9000076076491</v>
+        <v>684.9000076076422</v>
       </c>
       <c r="K11" t="n">
-        <v>537.7603945757943</v>
+        <v>537.7603945757245</v>
       </c>
       <c r="L11" t="n">
-        <v>537.7603945757903</v>
+        <v>537.7603945758004</v>
       </c>
       <c r="M11" t="n">
-        <v>693.5167202055742</v>
+        <v>693.5167202054955</v>
       </c>
       <c r="N11" t="n">
-        <v>693.5167202055896</v>
+        <v>693.5167202055829</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2216070221405282</v>
+        <v>0.221607022140527</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2216070221405289</v>
+        <v>0.221607022140528</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2219598116338963</v>
+        <v>0.2219598116338948</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2219598116338962</v>
+        <v>0.2219598116338964</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2252715943205368</v>
+        <v>0.2252715943205352</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2252715943205371</v>
+        <v>0.225271594320537</v>
       </c>
       <c r="U11" t="n">
-        <v>3.321360497066224</v>
+        <v>3.321360497065732</v>
       </c>
       <c r="V11" t="n">
-        <v>3.321360497066278</v>
+        <v>3.321360497066309</v>
       </c>
       <c r="W11" t="n">
-        <v>1.920472220754318</v>
+        <v>1.92047222075394</v>
       </c>
       <c r="X11" t="n">
-        <v>1.920472220754241</v>
+        <v>1.920472220754359</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.404686044280208</v>
+        <v>3.404686044279716</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.404686044280275</v>
+        <v>3.40468604428029</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>0.2876926816765709</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>0.2876926816766076</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>0.2258865940962132</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>0.2258865940962451</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>0.2913121372569515</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>0.2913121372569881</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02467646364099441</v>
+        <v>0.0246764636409912</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0246764636409948</v>
+        <v>0.02467646364099493</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.01873837522834602</v>
+        <v>0.01873837522834318</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0187383752283457</v>
+        <v>0.01873837522834639</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.02489214329146311</v>
+        <v>0.02489214329145989</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0248921432914635</v>
+        <v>0.02489214329146362</v>
       </c>
     </row>
     <row r="12">
@@ -2951,22 +2951,22 @@
         <v>0.5835968813275964</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>0.1410572422076466</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>0.1410572422076352</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>0.1133991134111392</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>0.1133991134111319</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>0.1351392741546293</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>0.1351392741546178</v>
       </c>
       <c r="AG12" t="n">
         <v>0.03448261318492422</v>
@@ -2981,7 +2981,7 @@
         <v>0.03336561325339464</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.03425330089856233</v>
+        <v>0.03425330089856232</v>
       </c>
       <c r="AL12" t="n">
         <v>0.03425330089856186</v>
@@ -2997,112 +2997,112 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.215414648670439</v>
+        <v>1.215414648670441</v>
       </c>
       <c r="D13" t="n">
-        <v>1.215414648670426</v>
+        <v>1.21541464867044</v>
       </c>
       <c r="E13" t="n">
-        <v>1.197550161296834</v>
+        <v>1.197550161296837</v>
       </c>
       <c r="F13" t="n">
-        <v>1.197550161296821</v>
+        <v>1.197550161296837</v>
       </c>
       <c r="G13" t="n">
-        <v>1.205536638909188</v>
+        <v>1.205536638909191</v>
       </c>
       <c r="H13" t="n">
-        <v>1.205536638909173</v>
+        <v>1.205536638909189</v>
       </c>
       <c r="I13" t="n">
-        <v>619.271184786008</v>
+        <v>619.2711847860421</v>
       </c>
       <c r="J13" t="n">
-        <v>619.2711847858455</v>
+        <v>619.2711847860321</v>
       </c>
       <c r="K13" t="n">
-        <v>510.9781770918903</v>
+        <v>510.9781770919314</v>
       </c>
       <c r="L13" t="n">
-        <v>510.9781770917572</v>
+        <v>510.9781770919462</v>
       </c>
       <c r="M13" t="n">
-        <v>604.1847184477541</v>
+        <v>604.1847184477883</v>
       </c>
       <c r="N13" t="n">
-        <v>604.1847184475915</v>
+        <v>604.1847184477781</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01866143787839246</v>
+        <v>0.01866143787839267</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01866143787839143</v>
+        <v>0.01866143787839261</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01807317154947878</v>
+        <v>0.01807317154947907</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01807317154947786</v>
+        <v>0.01807317154947915</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01871208975846715</v>
+        <v>0.01871208975846738</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01871208975846603</v>
+        <v>0.0187120897584673</v>
       </c>
       <c r="U13" t="n">
-        <v>4.181440045729967</v>
+        <v>4.181440045730522</v>
       </c>
       <c r="V13" t="n">
-        <v>4.181440045728492</v>
+        <v>4.181440045730588</v>
       </c>
       <c r="W13" t="n">
-        <v>1.770690826555561</v>
+        <v>1.770690826556224</v>
       </c>
       <c r="X13" t="n">
-        <v>1.770690826554862</v>
+        <v>1.770690826556533</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.540944914621419</v>
+        <v>3.540944914621799</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.540944914620177</v>
+        <v>3.540944914621798</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>0.2601252531131649</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>0.2601252531131606</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>0.2146367066913753</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>0.2146367066913815</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>0.2537881733793849</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>0.2537881733793806</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01025643025501718</v>
+        <v>0.01025643025501777</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.01025643025501447</v>
+        <v>0.01025643025501761</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.00845723734998324</v>
+        <v>0.008457237349983939</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.008457237349981014</v>
+        <v>0.00845723734998419</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.01001087802668609</v>
+        <v>0.01001087802668667</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01001087802668337</v>
+        <v>0.01001087802668651</v>
       </c>
     </row>
     <row r="14">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.264628069292651</v>
+        <v>1.264628069292649</v>
       </c>
       <c r="D14" t="n">
         <v>1.264628069292649</v>
@@ -3133,7 +3133,7 @@
         <v>1.254971400872742</v>
       </c>
       <c r="I14" t="n">
-        <v>1196.201767831253</v>
+        <v>1196.201767831233</v>
       </c>
       <c r="J14" t="n">
         <v>1196.201767831233</v>
@@ -3151,7 +3151,7 @@
         <v>1181.115301492979</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02231289726475477</v>
+        <v>0.02231289726475464</v>
       </c>
       <c r="P14" t="n">
         <v>0.02231289726475464</v>
@@ -3169,7 +3169,7 @@
         <v>0.02266687071555154</v>
       </c>
       <c r="U14" t="n">
-        <v>5.104851645040296</v>
+        <v>5.104851645040209</v>
       </c>
       <c r="V14" t="n">
         <v>5.104851645040209</v>
@@ -3187,25 +3187,25 @@
         <v>5.633230032435653</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>0.5024653096672357</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>0.5024653096672357</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>0.09333458837574445</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>0.09332718702412404</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>0.4961282299334557</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>0.4961282299334556</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.01959602438352617</v>
+        <v>0.01959602438352584</v>
       </c>
       <c r="AH14" t="n">
         <v>0.01959602438352584</v>
@@ -3251,7 +3251,7 @@
         <v>2.097121851084932</v>
       </c>
       <c r="I15" t="n">
-        <v>335.1276846846325</v>
+        <v>335.1276846846326</v>
       </c>
       <c r="J15" t="n">
         <v>335.1276846845912</v>
@@ -3305,22 +3305,22 @@
         <v>0.5222816079107214</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>0.1407705960579095</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>0.1407705960578921</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>0.1265657685980982</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>0.1265657685980758</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>0.1350119750084467</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>0.1350119750084293</v>
       </c>
       <c r="AG15" t="n">
         <v>0.02122330093920573</v>
@@ -3423,22 +3423,22 @@
         <v>0.5835968813275964</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>0.1410572422076466</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>0.1410572422076352</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>0.1133991134111392</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>0.1133991134111319</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>0.1351392741546293</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.1351392741546178</v>
       </c>
       <c r="AG16" t="n">
         <v>0.03448261318492422</v>
@@ -3541,22 +3541,22 @@
         <v>0.0845625937265025</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>0.01761574919806055</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>0.01761574919806055</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>0.01761574919806055</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>0.01761574919806055</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>0.01761574919806055</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>0.01761574919806055</v>
       </c>
       <c r="AG17" t="n">
         <v>0.002642390220925374</v>
@@ -3659,22 +3659,22 @@
         <v>0.0522812462324321</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>0.01284928529010889</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>0.01284928529010889</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>0.01284928529010889</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>0.01284928529010889</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>0.01284928529010889</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.01284928529010889</v>
       </c>
       <c r="AG18" t="n">
         <v>0.00168109002871214</v>
@@ -3703,112 +3703,112 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>21.81223996439661</v>
+        <v>21.81223996439659</v>
       </c>
       <c r="D19" t="n">
-        <v>21.81223996439635</v>
+        <v>21.81223996439638</v>
       </c>
       <c r="E19" t="n">
-        <v>22.48850242640301</v>
+        <v>22.488502426403</v>
       </c>
       <c r="F19" t="n">
-        <v>22.48837179885023</v>
+        <v>22.48837179885026</v>
       </c>
       <c r="G19" t="n">
-        <v>21.53183246107695</v>
+        <v>21.53183246107693</v>
       </c>
       <c r="H19" t="n">
-        <v>21.53183246107675</v>
+        <v>21.53183246107677</v>
       </c>
       <c r="I19" t="n">
-        <v>6844.96581739191</v>
+        <v>6844.965817391977</v>
       </c>
       <c r="J19" t="n">
-        <v>6844.965817391669</v>
+        <v>6844.965817391885</v>
       </c>
       <c r="K19" t="n">
-        <v>5242.223667553793</v>
+        <v>5242.223667553916</v>
       </c>
       <c r="L19" t="n">
-        <v>5242.206047412008</v>
+        <v>5242.206047412269</v>
       </c>
       <c r="M19" t="n">
-        <v>6850.849475311976</v>
+        <v>6850.849475312064</v>
       </c>
       <c r="N19" t="n">
-        <v>6850.849475311753</v>
+        <v>6850.84947531197</v>
       </c>
       <c r="O19" t="n">
-        <v>1.456344821276921</v>
+        <v>1.45634482127692</v>
       </c>
       <c r="P19" t="n">
-        <v>1.456344821276915</v>
+        <v>1.456344821276916</v>
       </c>
       <c r="Q19" t="n">
         <v>1.468968287822269</v>
       </c>
       <c r="R19" t="n">
-        <v>1.468966536458868</v>
+        <v>1.46896653645887</v>
       </c>
       <c r="S19" t="n">
-        <v>1.467618076002955</v>
+        <v>1.467618076002954</v>
       </c>
       <c r="T19" t="n">
-        <v>1.467618076002949</v>
+        <v>1.467618076002951</v>
       </c>
       <c r="U19" t="n">
-        <v>29.19735483603938</v>
+        <v>29.19735483604114</v>
       </c>
       <c r="V19" t="n">
-        <v>29.1973548360385</v>
+        <v>29.19735483604121</v>
       </c>
       <c r="W19" t="n">
-        <v>15.27450936653538</v>
+        <v>15.2745093665372</v>
       </c>
       <c r="X19" t="n">
-        <v>15.27448835365636</v>
+        <v>15.27448835365928</v>
       </c>
       <c r="Y19" t="n">
-        <v>27.74544823479609</v>
+        <v>27.74544823479723</v>
       </c>
       <c r="Z19" t="n">
-        <v>27.7454482347953</v>
+        <v>27.74544823479732</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.875232223852346</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.875232223852308</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.201999369419103</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.201991968067452</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.877703658085513</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.877703658085473</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.3056420782375144</v>
+        <v>0.3056420782375127</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.3056420782375103</v>
+        <v>0.3056420782375154</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.2723087476335246</v>
+        <v>0.2723087476335245</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.2723084592698045</v>
+        <v>0.2723084592698104</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.305953786407249</v>
+        <v>0.3059537864072475</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.3059537864072451</v>
+        <v>0.3059537864072503</v>
       </c>
     </row>
   </sheetData>
@@ -3904,16 +3904,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.947581187570586</v>
+        <v>3.947581187572543</v>
       </c>
       <c r="D4" t="n">
-        <v>3.947577293964415</v>
+        <v>3.947577293964662</v>
       </c>
       <c r="E4" t="n">
-        <v>4.18144004572844</v>
+        <v>4.181440045730522</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9440721723615879</v>
+        <v>0.944072172361586</v>
       </c>
     </row>
     <row r="5">
@@ -3948,16 +3948,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.135300417385556</v>
+        <v>3.135300417385277</v>
       </c>
       <c r="D6" t="n">
-        <v>3.135297382033347</v>
+        <v>3.135297382033655</v>
       </c>
       <c r="E6" t="n">
-        <v>3.321360497066028</v>
+        <v>3.321360497065732</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9439807633513944</v>
+        <v>0.9439807633513947</v>
       </c>
     </row>
     <row r="7">
@@ -4036,16 +4036,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.270570370291008</v>
+        <v>3.270570370290523</v>
       </c>
       <c r="D10" t="n">
-        <v>3.270567565536872</v>
+        <v>3.270567565536901</v>
       </c>
       <c r="E10" t="n">
-        <v>3.321360497066224</v>
+        <v>3.321360497065732</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9847080355113276</v>
+        <v>0.9847080355113277</v>
       </c>
     </row>
     <row r="11">
@@ -4080,16 +4080,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3.868201876088389</v>
+        <v>3.868201876088901</v>
       </c>
       <c r="D12" t="n">
-        <v>3.868190050769674</v>
+        <v>3.868190050771602</v>
       </c>
       <c r="E12" t="n">
-        <v>4.181440045729967</v>
+        <v>4.181440045730522</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9250884465122363</v>
+        <v>0.9250884465122358</v>
       </c>
     </row>
     <row r="13">
@@ -4102,16 +4102,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.718007585079172</v>
+        <v>4.718007585079092</v>
       </c>
       <c r="D13" t="n">
         <v>4.717993951579827</v>
       </c>
       <c r="E13" t="n">
-        <v>5.104851645040296</v>
+        <v>5.104851645040209</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9242203129767799</v>
+        <v>0.92422031297678</v>
       </c>
     </row>
     <row r="14">
@@ -4441,58 +4441,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.965394307439615</v>
+        <v>4.965394307439629</v>
       </c>
       <c r="C4" t="n">
-        <v>5.111475925128234</v>
+        <v>5.111475925128247</v>
       </c>
       <c r="D4" t="n">
-        <v>5.081602833500307</v>
+        <v>5.081602833500321</v>
       </c>
       <c r="E4" t="n">
-        <v>1332.14616699492</v>
+        <v>1332.14616699511</v>
       </c>
       <c r="F4" t="n">
-        <v>1306.95908935554</v>
+        <v>1306.959089355727</v>
       </c>
       <c r="G4" t="n">
-        <v>1364.975641046842</v>
+        <v>1364.975641047032</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3996213971670751</v>
+        <v>0.3996213971670763</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4055238214259677</v>
+        <v>0.4055238214259688</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4047000308204811</v>
+        <v>0.4047000308204823</v>
       </c>
       <c r="K4" t="n">
-        <v>5.615955500928096</v>
+        <v>5.615955500930178</v>
       </c>
       <c r="L4" t="n">
-        <v>4.085439338480557</v>
+        <v>4.085439338482216</v>
       </c>
       <c r="M4" t="n">
-        <v>4.972217066828541</v>
+        <v>4.972217066830099</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.5595688405767815</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.5489889926731703</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.5733588819304393</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0686047346000699</v>
+        <v>0.06860473460007309</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06825902827555004</v>
+        <v>0.06825902827555319</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06923095120437682</v>
+        <v>0.06923095120438001</v>
       </c>
     </row>
     <row r="5">
@@ -4502,58 +4502,58 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.462742325238724</v>
+        <v>2.46274232523871</v>
       </c>
       <c r="C5" t="n">
-        <v>2.443588105984543</v>
+        <v>2.443588105984536</v>
       </c>
       <c r="D5" t="n">
-        <v>2.481172352371113</v>
+        <v>2.481172352371098</v>
       </c>
       <c r="E5" t="n">
-        <v>715.4898562671651</v>
+        <v>715.4898562671077</v>
       </c>
       <c r="F5" t="n">
-        <v>576.1412345275061</v>
+        <v>576.1412345274712</v>
       </c>
       <c r="G5" t="n">
-        <v>726.6582882090122</v>
+        <v>726.6582882089548</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3142863803465565</v>
+        <v>0.314286380346555</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3157114664613613</v>
+        <v>0.3157114664613606</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3188812221807105</v>
+        <v>0.3188812221807093</v>
       </c>
       <c r="K5" t="n">
-        <v>3.37364174329846</v>
+        <v>3.373641743298164</v>
       </c>
       <c r="L5" t="n">
-        <v>1.985698421900861</v>
+        <v>1.985698421900734</v>
       </c>
       <c r="M5" t="n">
-        <v>3.390901123639189</v>
+        <v>3.390901123638882</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.3005419669666798</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.2420084902096152</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.3052332738724804</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02635755366970532</v>
+        <v>0.02635755366970334</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02069084026312756</v>
+        <v>0.02069084026312638</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02663710384271176</v>
+        <v>0.02663710384270977</v>
       </c>
     </row>
     <row r="6">
@@ -4569,7 +4569,7 @@
         <v>2.553889245679951</v>
       </c>
       <c r="D6" t="n">
-        <v>2.50140876603294</v>
+        <v>2.501408766032941</v>
       </c>
       <c r="E6" t="n">
         <v>955.0812780359004</v>
@@ -4596,25 +4596,25 @@
         <v>3.291589533651972</v>
       </c>
       <c r="M6" t="n">
-        <v>4.452359315415589</v>
+        <v>4.45235931541559</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.4011824953208015</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.3779472980145887</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.4084206491522775</v>
       </c>
       <c r="Q6" t="n">
         <v>0.04473904343994156</v>
       </c>
       <c r="R6" t="n">
-        <v>0.04379454308317475</v>
+        <v>0.04379454308317476</v>
       </c>
       <c r="S6" t="n">
-        <v>0.04501951092291294</v>
+        <v>0.04501951092291295</v>
       </c>
     </row>
     <row r="7">
@@ -4624,58 +4624,58 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.643142702480883</v>
+        <v>4.64314270248086</v>
       </c>
       <c r="C7" t="n">
-        <v>4.646217846762086</v>
+        <v>4.646217846762069</v>
       </c>
       <c r="D7" t="n">
-        <v>4.699963487562009</v>
+        <v>4.699963487561989</v>
       </c>
       <c r="E7" t="n">
-        <v>1020.027692292266</v>
+        <v>1020.027692292187</v>
       </c>
       <c r="F7" t="n">
-        <v>884.9392642450191</v>
+        <v>884.9392642449493</v>
       </c>
       <c r="G7" t="n">
-        <v>1036.741507759294</v>
+        <v>1036.741507759215</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4267071483514289</v>
+        <v>0.4267071483514276</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4307477289053144</v>
+        <v>0.4307477289053129</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4335687034902939</v>
+        <v>0.4335687034902922</v>
       </c>
       <c r="K7" t="n">
-        <v>3.952553723239276</v>
+        <v>3.952553723238783</v>
       </c>
       <c r="L7" t="n">
-        <v>2.602916118860147</v>
+        <v>2.602916118859769</v>
       </c>
       <c r="M7" t="n">
-        <v>4.066320411289567</v>
+        <v>4.066320411289074</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.4284632777344803</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.3717192980342329</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.4354839264997696</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04589976458020013</v>
+        <v>0.04589976458019693</v>
       </c>
       <c r="R7" t="n">
-        <v>0.04023615142248808</v>
+        <v>0.04023615142248524</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04631811784856706</v>
+        <v>0.04631811784856384</v>
       </c>
     </row>
     <row r="8">
@@ -4685,58 +4685,58 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.464797856266254</v>
+        <v>2.464797856266256</v>
       </c>
       <c r="C8" t="n">
-        <v>2.500694907676134</v>
+        <v>2.500694907676137</v>
       </c>
       <c r="D8" t="n">
-        <v>2.31056420428104</v>
+        <v>2.310564204281043</v>
       </c>
       <c r="E8" t="n">
-        <v>955.08127803589</v>
+        <v>955.0812780359241</v>
       </c>
       <c r="F8" t="n">
-        <v>780.9435206152749</v>
+        <v>780.9435206153159</v>
       </c>
       <c r="G8" t="n">
-        <v>925.9061100285073</v>
+        <v>925.9061100285414</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03565943660486598</v>
+        <v>0.03565943660486619</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03592507101206861</v>
+        <v>0.03592507101206889</v>
       </c>
       <c r="J8" t="n">
-        <v>0.034524292148795</v>
+        <v>0.03452429214879524</v>
       </c>
       <c r="K8" t="n">
-        <v>4.900199681030069</v>
+        <v>4.900199681030624</v>
       </c>
       <c r="L8" t="n">
-        <v>2.18118295476407</v>
+        <v>2.181182954764733</v>
       </c>
       <c r="M8" t="n">
-        <v>4.124541795949079</v>
+        <v>4.124541795949459</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.4011824953208115</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.3280358201025145</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.3889274475340142</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.04473904343994139</v>
+        <v>0.04473904343994198</v>
       </c>
       <c r="R8" t="n">
-        <v>0.04182285060337818</v>
+        <v>0.04182285060337886</v>
       </c>
       <c r="S8" t="n">
-        <v>0.04426417892524841</v>
+        <v>0.04426417892524899</v>
       </c>
     </row>
     <row r="9">
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.811364916704877</v>
+        <v>4.811364916704875</v>
       </c>
       <c r="C9" t="n">
         <v>5.232636395172063</v>
@@ -4755,7 +4755,7 @@
         <v>4.457120817329539</v>
       </c>
       <c r="E9" t="n">
-        <v>1867.139545765768</v>
+        <v>1867.139545765748</v>
       </c>
       <c r="F9" t="n">
         <v>793.4745106199844</v>
@@ -4764,7 +4764,7 @@
         <v>1824.25502798415</v>
       </c>
       <c r="H9" t="n">
-        <v>0.244411022202129</v>
+        <v>0.2444110222021288</v>
       </c>
       <c r="I9" t="n">
         <v>0.2443717549904741</v>
@@ -4773,7 +4773,7 @@
         <v>0.2398936987284944</v>
       </c>
       <c r="K9" t="n">
-        <v>6.454804506513449</v>
+        <v>6.454804506513362</v>
       </c>
       <c r="L9" t="n">
         <v>1.127682998877772</v>
@@ -4782,16 +4782,16 @@
         <v>6.739108521674124</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.7842931479327917</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.3332994703849819</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.7662794790965317</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07530193850765612</v>
+        <v>0.07530193850765579</v>
       </c>
       <c r="R9" t="n">
         <v>0.05750533398580601</v>

--- a/openalaqs_standalone/validation/data/training_validation_reference.xlsx
+++ b/openalaqs_standalone/validation/data/training_validation_reference.xlsx
@@ -1433,28 +1433,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.875232223852346</v>
+        <v>1.642661828468681</v>
       </c>
       <c r="C7" t="n">
-        <v>2.875232223852308</v>
+        <v>1.642661828468659</v>
       </c>
       <c r="D7" t="n">
-        <v>2.201999369419103</v>
+        <v>1.258034144320518</v>
       </c>
       <c r="E7" t="n">
-        <v>2.201991968067452</v>
+        <v>1.258029915821082</v>
       </c>
       <c r="F7" t="n">
-        <v>2.877703658085513</v>
+        <v>1.644073794654478</v>
       </c>
       <c r="G7" t="n">
-        <v>2.877703658085473</v>
+        <v>1.644073794654455</v>
       </c>
       <c r="H7" t="n">
-        <v>2.875232223852346</v>
+        <v>1.642661828468681</v>
       </c>
       <c r="I7" t="n">
-        <v>2.875232223852308</v>
+        <v>1.642661828468659</v>
       </c>
     </row>
     <row r="8">
@@ -2007,22 +2007,22 @@
         <v>0.7536837466261775</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1410572422076466</v>
+        <v>0.08058804623896061</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1410572422076352</v>
+        <v>0.08058804623895412</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1325574643457678</v>
+        <v>0.07573199999395004</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1325574643457592</v>
+        <v>0.07573199999394514</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.1455876365944061</v>
+        <v>0.08317632619259424</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1455876365943946</v>
+        <v>0.08317632619258769</v>
       </c>
       <c r="AG4" t="n">
         <v>0.03448261318492422</v>
@@ -2125,22 +2125,22 @@
         <v>3.479763630922331</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2601252531131649</v>
+        <v>0.148613326035015</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2601252531131606</v>
+        <v>0.1486133260350125</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.2508673931013095</v>
+        <v>0.1433241764739385</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.2508673931013168</v>
+        <v>0.1433241764739427</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.2649764909362088</v>
+        <v>0.1513849084924697</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2649764909362045</v>
+        <v>0.1513849084924672</v>
       </c>
       <c r="AG5" t="n">
         <v>0.01025643025501777</v>
@@ -2243,22 +2243,22 @@
         <v>0.6542070955548853</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1407705960579095</v>
+        <v>0.08042428114042539</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1407705960578921</v>
+        <v>0.08042428114041549</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1479483860280324</v>
+        <v>0.08452505654871176</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.1479483860280062</v>
+        <v>0.08452505654869683</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1451790052017638</v>
+        <v>0.08294286915735413</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1451790052017465</v>
+        <v>0.08294286915734421</v>
       </c>
       <c r="AG6" t="n">
         <v>0.02122330093920573</v>
@@ -2361,22 +2361,22 @@
         <v>3.338619877407011</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2876926816765709</v>
+        <v>0.164362997395289</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2876926816766076</v>
+        <v>0.16436299739531</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2291592049195063</v>
+        <v>0.1309219740376826</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.2291592049195386</v>
+        <v>0.1309219740377011</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.2923839885823716</v>
+        <v>0.1670432090024979</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2923839885824082</v>
+        <v>0.1670432090025189</v>
       </c>
       <c r="AG7" t="n">
         <v>0.0246764636409912</v>
@@ -2479,22 +2479,22 @@
         <v>0.7606117009602785</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.1410572422076466</v>
+        <v>0.08058804623896061</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1410572422076352</v>
+        <v>0.08058804623895412</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.1306618442854375</v>
+        <v>0.07464900478801434</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.1306618442854291</v>
+        <v>0.07464900478800951</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.1445525499275927</v>
+        <v>0.08258496618256586</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1445525499275812</v>
+        <v>0.08258496618255931</v>
       </c>
       <c r="AG8" t="n">
         <v>0.03448261318492422</v>
@@ -2597,22 +2597,22 @@
         <v>3.691747614454787</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.2601252531131549</v>
+        <v>0.1486133260350092</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.2601252531131489</v>
+        <v>0.1486133260350058</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.2472854537291511</v>
+        <v>0.1412777626122261</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.2472854537291488</v>
+        <v>0.1412777626122248</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.2638680992246848</v>
+        <v>0.1507516682482879</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.2638680992246788</v>
+        <v>0.1507516682482845</v>
       </c>
       <c r="AG9" t="n">
         <v>0.01025643025501734</v>
@@ -2715,22 +2715,22 @@
         <v>0.6616343670092529</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.1407705960579095</v>
+        <v>0.08042428114042539</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.1407705960578921</v>
+        <v>0.08042428114041549</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1458327039380197</v>
+        <v>0.08331633671675945</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1458327039379939</v>
+        <v>0.08331633671674472</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.1441717892428182</v>
+        <v>0.08236743208654677</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1441717892428007</v>
+        <v>0.08236743208653685</v>
       </c>
       <c r="AG10" t="n">
         <v>0.02122330093920573</v>
@@ -2833,22 +2833,22 @@
         <v>3.40468604428029</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.2876926816765709</v>
+        <v>0.164362997395289</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2876926816766076</v>
+        <v>0.16436299739531</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.2258865940962132</v>
+        <v>0.1290522840577705</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.2258865940962451</v>
+        <v>0.1290522840577888</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.2913121372569515</v>
+        <v>0.1664308448103277</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.2913121372569881</v>
+        <v>0.1664308448103486</v>
       </c>
       <c r="AG11" t="n">
         <v>0.0246764636409912</v>
@@ -2951,22 +2951,22 @@
         <v>0.5835968813275964</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1410572422076466</v>
+        <v>0.08058804623896061</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.1410572422076352</v>
+        <v>0.08058804623895412</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1133991134111392</v>
+        <v>0.06478655652136821</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1133991134111319</v>
+        <v>0.06478655652136402</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.1351392741546293</v>
+        <v>0.07720702534536339</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1351392741546178</v>
+        <v>0.07720702534535687</v>
       </c>
       <c r="AG12" t="n">
         <v>0.03448261318492422</v>
@@ -3069,22 +3069,22 @@
         <v>3.540944914621798</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2601252531131649</v>
+        <v>0.148613326035015</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.2601252531131606</v>
+        <v>0.1486133260350125</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.2146367066913753</v>
+        <v>0.122625060384777</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.2146367066913815</v>
+        <v>0.1226250603847805</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.2537881733793849</v>
+        <v>0.1449928605657265</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.2537881733793806</v>
+        <v>0.1449928605657241</v>
       </c>
       <c r="AG13" t="n">
         <v>0.01025643025501777</v>
@@ -3187,22 +3187,22 @@
         <v>5.633230032435653</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.5024653096672357</v>
+        <v>0.2870657115877016</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.5024653096672357</v>
+        <v>0.2870657115877016</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.09333458837574445</v>
+        <v>0.05332340265554335</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.09332718702412404</v>
+        <v>0.0533191741561251</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.4961282299334557</v>
+        <v>0.2834452461184132</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.4961282299334556</v>
+        <v>0.2834452461184131</v>
       </c>
       <c r="AG14" t="n">
         <v>0.01959602438352584</v>
@@ -3305,22 +3305,22 @@
         <v>0.5222816079107214</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.1407705960579095</v>
+        <v>0.08042428114042539</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.1407705960578921</v>
+        <v>0.08042428114041549</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1265657685980982</v>
+        <v>0.07230885740016404</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.1265657685980758</v>
+        <v>0.07230885740015125</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.1350119750084467</v>
+        <v>0.0771342974987234</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1350119750084293</v>
+        <v>0.07713429749871348</v>
       </c>
       <c r="AG15" t="n">
         <v>0.02122330093920573</v>
@@ -3423,22 +3423,22 @@
         <v>0.5835968813275964</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.1410572422076466</v>
+        <v>0.08058804623896061</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.1410572422076352</v>
+        <v>0.08058804623895412</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1133991134111392</v>
+        <v>0.06478655652136821</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.1133991134111319</v>
+        <v>0.06478655652136402</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.1351392741546293</v>
+        <v>0.07720702534536339</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.1351392741546178</v>
+        <v>0.07720702534535687</v>
       </c>
       <c r="AG16" t="n">
         <v>0.03448261318492422</v>
@@ -3541,22 +3541,22 @@
         <v>0.0845625937265025</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.01761574919806055</v>
+        <v>0.01006413274986231</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.01761574919806055</v>
+        <v>0.01006413274986231</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.01761574919806055</v>
+        <v>0.01006413274986231</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.01761574919806055</v>
+        <v>0.01006413274986231</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.01761574919806055</v>
+        <v>0.01006413274986231</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.01761574919806055</v>
+        <v>0.01006413274986231</v>
       </c>
       <c r="AG17" t="n">
         <v>0.002642390220925374</v>
@@ -3659,22 +3659,22 @@
         <v>0.0522812462324321</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.01284928529010889</v>
+        <v>0.007340982858381433</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.01284928529010889</v>
+        <v>0.007340982858381432</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.01284928529010889</v>
+        <v>0.007340982858381433</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.01284928529010889</v>
+        <v>0.007340982858381432</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.01284928529010889</v>
+        <v>0.007340982858381433</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.01284928529010889</v>
+        <v>0.007340982858381432</v>
       </c>
       <c r="AG18" t="n">
         <v>0.00168109002871214</v>
@@ -3775,22 +3775,22 @@
         <v>27.74544823479732</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.875232223852346</v>
+        <v>1.642661828468681</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.875232223852308</v>
+        <v>1.642661828468659</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.201999369419103</v>
+        <v>1.258034144320518</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.201991968067452</v>
+        <v>1.258029915821082</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.877703658085513</v>
+        <v>1.644073794654478</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.877703658085473</v>
+        <v>1.644073794654455</v>
       </c>
       <c r="AG19" t="n">
         <v>0.3056420782375127</v>
@@ -4477,13 +4477,13 @@
         <v>4.972217066830099</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5595688405767815</v>
+        <v>0.3196897861642632</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5489889926731703</v>
+        <v>0.3136453657664626</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5733588819304393</v>
+        <v>0.3275682365922803</v>
       </c>
       <c r="Q4" t="n">
         <v>0.06860473460007309</v>
@@ -4538,13 +4538,13 @@
         <v>3.390901123638882</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3005419669666798</v>
+        <v>0.1717039802536704</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2420084902096152</v>
+        <v>0.138262956896064</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3052332738724804</v>
+        <v>0.1743841918608794</v>
       </c>
       <c r="Q5" t="n">
         <v>0.02635755366970334</v>
@@ -4599,13 +4599,13 @@
         <v>4.45235931541559</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4011824953208015</v>
+        <v>0.2292013722739699</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3779472980145887</v>
+        <v>0.2159267674002405</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4084206491522775</v>
+        <v>0.2333366344308538</v>
       </c>
       <c r="Q6" t="n">
         <v>0.04473904343994156</v>
@@ -4660,13 +4660,13 @@
         <v>4.066320411289074</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4284632777344803</v>
+        <v>0.2447872785357144</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3717192980342329</v>
+        <v>0.21236862077453</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4354839264997696</v>
+        <v>0.2487982768968744</v>
       </c>
       <c r="Q7" t="n">
         <v>0.04589976458019693</v>
@@ -4721,13 +4721,13 @@
         <v>4.124541795949459</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4011824953208115</v>
+        <v>0.2292013722739756</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3280358201025145</v>
+        <v>0.1874116169061452</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3889274475340142</v>
+        <v>0.2221998859110899</v>
       </c>
       <c r="Q8" t="n">
         <v>0.04473904343994198</v>
@@ -4782,13 +4782,13 @@
         <v>6.739108521674124</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7842931479327917</v>
+        <v>0.4480780389670875</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3332994703849819</v>
+        <v>0.1904188165770756</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7662794790965317</v>
+        <v>0.4377865689625</v>
       </c>
       <c r="Q9" t="n">
         <v>0.07530193850765579</v>

--- a/openalaqs_standalone/validation/data/training_validation_reference.xlsx
+++ b/openalaqs_standalone/validation/data/training_validation_reference.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Made on 2026-10-19 by openalaqs_standalone/validation/tools/regenerate_training_validation_xlsx.py</t>
+          <t>Made on 2026-10-20 by openalaqs_standalone/validation/tools/regenerate_training_validation_xlsx.py</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Worst relative gap plugin vs reference: 3.0e-13 on the ANP and helicopter movements, 8.0e-05 on movement 11 (CUSTOM profile, supplied track).</t>
+          <t>Worst relative gap plugin vs reference: 3.0e-13 on the ANP and helicopter movements, 1.3e-05 on movement 11 (CUSTOM profile, supplied track).</t>
         </is>
       </c>
     </row>
@@ -1315,10 +1315,10 @@
         <v>21.81223996439638</v>
       </c>
       <c r="D3" t="n">
-        <v>22.488502426403</v>
+        <v>22.05655953962632</v>
       </c>
       <c r="E3" t="n">
-        <v>22.48837179885026</v>
+        <v>22.05655898878842</v>
       </c>
       <c r="F3" t="n">
         <v>21.53183246107693</v>
@@ -1346,10 +1346,10 @@
         <v>6844.965817391885</v>
       </c>
       <c r="D4" t="n">
-        <v>5242.223667553916</v>
+        <v>5738.54009032065</v>
       </c>
       <c r="E4" t="n">
-        <v>5242.206047412269</v>
+        <v>5738.533661743943</v>
       </c>
       <c r="F4" t="n">
         <v>6850.849475312064</v>
@@ -1377,10 +1377,10 @@
         <v>1.456344821276916</v>
       </c>
       <c r="D5" t="n">
-        <v>1.468968287822269</v>
+        <v>1.466378563974153</v>
       </c>
       <c r="E5" t="n">
-        <v>1.46896653645887</v>
+        <v>1.466378519907129</v>
       </c>
       <c r="F5" t="n">
         <v>1.467618076002954</v>
@@ -1408,10 +1408,10 @@
         <v>29.19735483604121</v>
       </c>
       <c r="D6" t="n">
-        <v>15.2745093665372</v>
+        <v>16.87426788634922</v>
       </c>
       <c r="E6" t="n">
-        <v>15.27448835365928</v>
+        <v>16.8742442550353</v>
       </c>
       <c r="F6" t="n">
         <v>27.74544823479723</v>
@@ -1439,10 +1439,10 @@
         <v>1.642661828468659</v>
       </c>
       <c r="D7" t="n">
-        <v>1.258034144320518</v>
+        <v>1.377140662054988</v>
       </c>
       <c r="E7" t="n">
-        <v>1.258029915821082</v>
+        <v>1.37713911931864</v>
       </c>
       <c r="F7" t="n">
         <v>1.644073794654478</v>
@@ -1470,10 +1470,10 @@
         <v>0.3056420782375154</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2723087476335245</v>
+        <v>0.2804553351872513</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2723084592698104</v>
+        <v>0.2804552299799123</v>
       </c>
       <c r="F8" t="n">
         <v>0.3059537864072475</v>
@@ -3121,10 +3121,10 @@
         <v>1.264628069292649</v>
       </c>
       <c r="E14" t="n">
-        <v>1.647275994818408</v>
+        <v>1.215333108041731</v>
       </c>
       <c r="F14" t="n">
-        <v>1.647145367265797</v>
+        <v>1.21533255720396</v>
       </c>
       <c r="G14" t="n">
         <v>1.254971400872743</v>
@@ -3139,10 +3139,10 @@
         <v>1196.201767831233</v>
       </c>
       <c r="K14" t="n">
-        <v>222.1984233872894</v>
+        <v>718.5148461540236</v>
       </c>
       <c r="L14" t="n">
-        <v>222.1808032457149</v>
+        <v>718.5084175773893</v>
       </c>
       <c r="M14" t="n">
         <v>1181.115301492979</v>
@@ -3157,10 +3157,10 @@
         <v>0.02231289726475464</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02208553113718624</v>
+        <v>0.01949580728907056</v>
       </c>
       <c r="R14" t="n">
-        <v>0.02208377977379016</v>
+        <v>0.01949576322204896</v>
       </c>
       <c r="S14" t="n">
         <v>0.02266687071555156</v>
@@ -3175,10 +3175,10 @@
         <v>5.104851645040209</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2649824632874963</v>
+        <v>1.864740983099519</v>
       </c>
       <c r="X14" t="n">
-        <v>0.2649614504087965</v>
+        <v>1.864717351784814</v>
       </c>
       <c r="Y14" t="n">
         <v>5.633230032435653</v>
@@ -3193,10 +3193,10 @@
         <v>0.2870657115877016</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.05332340265554335</v>
+        <v>0.1724299203900134</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0533191741561251</v>
+        <v>0.1724283776536827</v>
       </c>
       <c r="AE14" t="n">
         <v>0.2834452461184132</v>
@@ -3211,10 +3211,10 @@
         <v>0.01959602438352584</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.003624701124814137</v>
+        <v>0.01177128867854098</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.003624412761097652</v>
+        <v>0.01177118347119959</v>
       </c>
       <c r="AK14" t="n">
         <v>0.01935047215519474</v>
@@ -3709,10 +3709,10 @@
         <v>21.81223996439638</v>
       </c>
       <c r="E19" t="n">
-        <v>22.488502426403</v>
+        <v>22.05655953962632</v>
       </c>
       <c r="F19" t="n">
-        <v>22.48837179885026</v>
+        <v>22.05655898878842</v>
       </c>
       <c r="G19" t="n">
         <v>21.53183246107693</v>
@@ -3727,10 +3727,10 @@
         <v>6844.965817391885</v>
       </c>
       <c r="K19" t="n">
-        <v>5242.223667553916</v>
+        <v>5738.54009032065</v>
       </c>
       <c r="L19" t="n">
-        <v>5242.206047412269</v>
+        <v>5738.533661743943</v>
       </c>
       <c r="M19" t="n">
         <v>6850.849475312064</v>
@@ -3745,10 +3745,10 @@
         <v>1.456344821276916</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.468968287822269</v>
+        <v>1.466378563974153</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46896653645887</v>
+        <v>1.466378519907129</v>
       </c>
       <c r="S19" t="n">
         <v>1.467618076002954</v>
@@ -3763,10 +3763,10 @@
         <v>29.19735483604121</v>
       </c>
       <c r="W19" t="n">
-        <v>15.2745093665372</v>
+        <v>16.87426788634922</v>
       </c>
       <c r="X19" t="n">
-        <v>15.27448835365928</v>
+        <v>16.8742442550353</v>
       </c>
       <c r="Y19" t="n">
         <v>27.74544823479723</v>
@@ -3781,10 +3781,10 @@
         <v>1.642661828468659</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.258034144320518</v>
+        <v>1.377140662054988</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.258029915821082</v>
+        <v>1.37713911931864</v>
       </c>
       <c r="AE19" t="n">
         <v>1.644073794654478</v>
@@ -3799,10 +3799,10 @@
         <v>0.3056420782375154</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.2723087476335245</v>
+        <v>0.2804553351872513</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.2723084592698104</v>
+        <v>0.2804552299799123</v>
       </c>
       <c r="AK19" t="n">
         <v>0.3059537864072475</v>
@@ -4749,7 +4749,7 @@
         <v>4.811364916704875</v>
       </c>
       <c r="C9" t="n">
-        <v>5.232636395172063</v>
+        <v>4.800693508395386</v>
       </c>
       <c r="D9" t="n">
         <v>4.457120817329539</v>
@@ -4758,7 +4758,7 @@
         <v>1867.139545765748</v>
       </c>
       <c r="F9" t="n">
-        <v>793.4745106199844</v>
+        <v>1289.790933386719</v>
       </c>
       <c r="G9" t="n">
         <v>1824.25502798415</v>
@@ -4767,7 +4767,7 @@
         <v>0.2444110222021288</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2443717549904741</v>
+        <v>0.2417820311423584</v>
       </c>
       <c r="J9" t="n">
         <v>0.2398936987284944</v>
@@ -4776,7 +4776,7 @@
         <v>6.454804506513362</v>
       </c>
       <c r="L9" t="n">
-        <v>1.127682998877772</v>
+        <v>2.727441518689794</v>
       </c>
       <c r="M9" t="n">
         <v>6.739108521674124</v>
@@ -4785,7 +4785,7 @@
         <v>0.4480780389670875</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1904188165770756</v>
+        <v>0.3095253343115457</v>
       </c>
       <c r="P9" t="n">
         <v>0.4377865689625</v>
@@ -4794,7 +4794,7 @@
         <v>0.07530193850765579</v>
       </c>
       <c r="R9" t="n">
-        <v>0.05750533398580601</v>
+        <v>0.06565192153953285</v>
       </c>
       <c r="S9" t="n">
         <v>0.07448392366343196</v>

--- a/openalaqs_standalone/validation/data/training_validation_reference.xlsx
+++ b/openalaqs_standalone/validation/data/training_validation_reference.xlsx
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Made on 2026-10-20 by openalaqs_standalone/validation/tools/regenerate_training_validation_xlsx.py</t>
+          <t>Made on 2026-10-24 by openalaqs_standalone/validation/tools/regenerate_training_validation_xlsx.py</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Worst relative gap plugin vs reference: 3.0e-13 on the ANP and helicopter movements, 1.3e-05 on movement 11 (CUSTOM profile, supplied track).</t>
+          <t>Worst relative gap plugin vs reference: 3.1e-13 on the ANP and helicopter movements, 1.2e-15 on movement 11 (CUSTOM profile, supplied track).</t>
         </is>
       </c>
     </row>
@@ -1315,16 +1315,16 @@
         <v>21.81223996439638</v>
       </c>
       <c r="D3" t="n">
-        <v>22.05655953962632</v>
+        <v>21.54564267489084</v>
       </c>
       <c r="E3" t="n">
-        <v>22.05655898878842</v>
+        <v>21.54564267489072</v>
       </c>
       <c r="F3" t="n">
-        <v>21.53183246107693</v>
+        <v>20.90758338800455</v>
       </c>
       <c r="G3" t="n">
-        <v>21.53183246107677</v>
+        <v>20.9075833880044</v>
       </c>
       <c r="H3" t="n">
         <v>21.81223996439659</v>
@@ -1346,16 +1346,16 @@
         <v>6844.965817391885</v>
       </c>
       <c r="D4" t="n">
-        <v>5738.54009032065</v>
+        <v>5513.466986269082</v>
       </c>
       <c r="E4" t="n">
-        <v>5738.533661743943</v>
+        <v>5513.46698626901</v>
       </c>
       <c r="F4" t="n">
-        <v>6850.849475312064</v>
+        <v>6803.837342074753</v>
       </c>
       <c r="G4" t="n">
-        <v>6850.84947531197</v>
+        <v>6803.837342074659</v>
       </c>
       <c r="H4" t="n">
         <v>6844.965817391977</v>
@@ -1377,16 +1377,16 @@
         <v>1.456344821276916</v>
       </c>
       <c r="D5" t="n">
-        <v>1.466378563974153</v>
+        <v>1.409206313085661</v>
       </c>
       <c r="E5" t="n">
-        <v>1.466378519907129</v>
+        <v>1.409206313085659</v>
       </c>
       <c r="F5" t="n">
-        <v>1.467618076002954</v>
+        <v>1.407030001059383</v>
       </c>
       <c r="G5" t="n">
-        <v>1.467618076002951</v>
+        <v>1.40703000105938</v>
       </c>
       <c r="H5" t="n">
         <v>1.45634482127692</v>
@@ -1408,16 +1408,16 @@
         <v>29.19735483604121</v>
       </c>
       <c r="D6" t="n">
-        <v>16.87426788634922</v>
+        <v>15.31064297240067</v>
       </c>
       <c r="E6" t="n">
-        <v>16.8742442550353</v>
+        <v>15.31064297240135</v>
       </c>
       <c r="F6" t="n">
-        <v>27.74544823479723</v>
+        <v>27.99025108737341</v>
       </c>
       <c r="G6" t="n">
-        <v>27.74544823479732</v>
+        <v>27.99025108737341</v>
       </c>
       <c r="H6" t="n">
         <v>27.96272566796256</v>
@@ -1439,16 +1439,16 @@
         <v>1.642661828468659</v>
       </c>
       <c r="D7" t="n">
-        <v>1.377140662054988</v>
+        <v>1.323127390622562</v>
       </c>
       <c r="E7" t="n">
-        <v>1.37713911931864</v>
+        <v>1.323127390622545</v>
       </c>
       <c r="F7" t="n">
-        <v>1.644073794654478</v>
+        <v>1.632791775312965</v>
       </c>
       <c r="G7" t="n">
-        <v>1.644073794654455</v>
+        <v>1.632791775312942</v>
       </c>
       <c r="H7" t="n">
         <v>1.642661828468681</v>
@@ -1470,16 +1470,16 @@
         <v>0.3056420782375154</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2804553351872513</v>
+        <v>0.2745527999750175</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2804552299799123</v>
+        <v>0.2745527999750196</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3059537864072475</v>
+        <v>0.3047732206655252</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3059537864072503</v>
+        <v>0.3047732206655279</v>
       </c>
       <c r="H8" t="n">
         <v>0.3056420782375127</v>
@@ -1941,16 +1941,16 @@
         <v>1.249383207595792</v>
       </c>
       <c r="E4" t="n">
-        <v>1.337250514293041</v>
+        <v>1.266408428570419</v>
       </c>
       <c r="F4" t="n">
-        <v>1.337250514293001</v>
+        <v>1.266408428570373</v>
       </c>
       <c r="G4" t="n">
-        <v>1.284589582542515</v>
+        <v>1.160272940755099</v>
       </c>
       <c r="H4" t="n">
-        <v>1.284589582542488</v>
+        <v>1.160272940755072</v>
       </c>
       <c r="I4" t="n">
         <v>335.810093249882</v>
@@ -1959,16 +1959,16 @@
         <v>335.8100932498548</v>
       </c>
       <c r="K4" t="n">
-        <v>315.5749663487118</v>
+        <v>276.0026242620052</v>
       </c>
       <c r="L4" t="n">
-        <v>315.5749663486914</v>
+        <v>276.0026242619869</v>
       </c>
       <c r="M4" t="n">
-        <v>346.5954463282931</v>
+        <v>327.9034077021497</v>
       </c>
       <c r="N4" t="n">
-        <v>346.5954463282657</v>
+        <v>327.9034077021224</v>
       </c>
       <c r="O4" t="n">
         <v>0.01699799872647352</v>
@@ -1977,16 +1977,16 @@
         <v>0.01699799872647318</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01831898487119018</v>
+        <v>0.01731715289631759</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01831898487118959</v>
+        <v>0.01731715289631693</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01747816171805254</v>
+        <v>0.0158127644321599</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01747816171805214</v>
+        <v>0.0158127644321595</v>
       </c>
       <c r="U4" t="n">
         <v>0.7187596353001016</v>
@@ -1995,16 +1995,16 @@
         <v>0.7187596353000264</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6236859001187546</v>
+        <v>0.517371231463934</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6236859001187076</v>
+        <v>0.5173712314638945</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7536837466262534</v>
+        <v>0.7247619341121828</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.7536837466261775</v>
+        <v>0.7247619341121069</v>
       </c>
       <c r="AA4" t="n">
         <v>0.08058804623896061</v>
@@ -2013,16 +2013,16 @@
         <v>0.08058804623895412</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.07573199999395004</v>
+        <v>0.06623538926672436</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.07573199999394514</v>
+        <v>0.06623538926671997</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.08317632619259424</v>
+        <v>0.07869059183444563</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.08317632619258769</v>
+        <v>0.07869059183443909</v>
       </c>
       <c r="AG4" t="n">
         <v>0.03448261318492422</v>
@@ -2031,16 +2031,16 @@
         <v>0.03448261318492375</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.03412611505773455</v>
+        <v>0.03346375134503373</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0341261150577342</v>
+        <v>0.03346375134503341</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.03465815909623058</v>
+        <v>0.03435392140174395</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.03465815909623011</v>
+        <v>0.03435392140174348</v>
       </c>
     </row>
     <row r="5">
@@ -2059,16 +2059,16 @@
         <v>1.21541464867044</v>
       </c>
       <c r="E5" t="n">
-        <v>1.22896439155961</v>
+        <v>1.094518729843992</v>
       </c>
       <c r="F5" t="n">
-        <v>1.22896439155961</v>
+        <v>1.094518729843992</v>
       </c>
       <c r="G5" t="n">
-        <v>1.231490660925495</v>
+        <v>1.100875537832215</v>
       </c>
       <c r="H5" t="n">
-        <v>1.231490660925493</v>
+        <v>1.100875537832213</v>
       </c>
       <c r="I5" t="n">
         <v>619.2711847860421</v>
@@ -2077,16 +2077,16 @@
         <v>619.2711847860321</v>
       </c>
       <c r="K5" t="n">
-        <v>597.2313179545397</v>
+        <v>527.2256563696022</v>
       </c>
       <c r="L5" t="n">
-        <v>597.2313179545572</v>
+        <v>527.2256563696229</v>
       </c>
       <c r="M5" t="n">
-        <v>630.8203587259069</v>
+        <v>610.8045461869442</v>
       </c>
       <c r="N5" t="n">
-        <v>630.8203587258967</v>
+        <v>610.804546186934</v>
       </c>
       <c r="O5" t="n">
         <v>0.01866143787839267</v>
@@ -2095,16 +2095,16 @@
         <v>0.01866143787839261</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01854634710651523</v>
+        <v>0.01650724818391685</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01854634710651532</v>
+        <v>0.01650724818391695</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01874844865578606</v>
+        <v>0.0170157928229747</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01874844865578599</v>
+        <v>0.01701579282297461</v>
       </c>
       <c r="U5" t="n">
         <v>4.181440045730522</v>
@@ -2113,16 +2113,16 @@
         <v>4.181440045730588</v>
       </c>
       <c r="W5" t="n">
-        <v>2.690133029619446</v>
+        <v>1.870353400893096</v>
       </c>
       <c r="X5" t="n">
-        <v>2.690133029619915</v>
+        <v>1.870353400893273</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.479763630922355</v>
+        <v>3.476152672202555</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.479763630922331</v>
+        <v>3.476152672202485</v>
       </c>
       <c r="AA5" t="n">
         <v>0.148613326035015</v>
@@ -2131,16 +2131,16 @@
         <v>0.1486133260350125</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1433241764739385</v>
+        <v>0.126524146914976</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.1433241764739427</v>
+        <v>0.126524146914981</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.1513849084924697</v>
+        <v>0.1465814935301922</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1513849084924672</v>
+        <v>0.1465814935301897</v>
       </c>
       <c r="AG5" t="n">
         <v>0.01025643025501777</v>
@@ -2149,16 +2149,16 @@
         <v>0.01025643025501761</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.009884808647925979</v>
+        <v>0.008726604098357583</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.009884808647926275</v>
+        <v>0.008726604098357937</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.01044440836286177</v>
+        <v>0.01011862449402184</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01044440836286161</v>
+        <v>0.01011862449402168</v>
       </c>
     </row>
     <row r="6">
@@ -2177,16 +2177,16 @@
         <v>2.297353639816358</v>
       </c>
       <c r="E6" t="n">
-        <v>2.342018207918636</v>
+        <v>2.167542418542522</v>
       </c>
       <c r="F6" t="n">
-        <v>2.342018207918633</v>
+        <v>2.167542418542526</v>
       </c>
       <c r="G6" t="n">
-        <v>2.36227977867535</v>
+        <v>2.130510741621854</v>
       </c>
       <c r="H6" t="n">
-        <v>2.362279778675288</v>
+        <v>2.130510741621792</v>
       </c>
       <c r="I6" t="n">
         <v>335.1276846846326</v>
@@ -2195,16 +2195,16 @@
         <v>335.1276846845912</v>
       </c>
       <c r="K6" t="n">
-        <v>352.2156007779217</v>
+        <v>309.9611164637622</v>
       </c>
       <c r="L6" t="n">
-        <v>352.2156007778595</v>
+        <v>309.9611164637063</v>
       </c>
       <c r="M6" t="n">
-        <v>345.6226317182782</v>
+        <v>327.4338942790829</v>
       </c>
       <c r="N6" t="n">
-        <v>345.6226317182368</v>
+        <v>327.4338942790415</v>
       </c>
       <c r="O6" t="n">
         <v>0.2051001262109007</v>
@@ -2213,16 +2213,16 @@
         <v>0.2051001262108993</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2097966550969539</v>
+        <v>0.191101498389304</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2097966550969528</v>
+        <v>0.1911014983893032</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2096115860953342</v>
+        <v>0.1873572884652835</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2096115860953324</v>
+        <v>0.1873572884652817</v>
       </c>
       <c r="U6" t="n">
         <v>0.6311932261730516</v>
@@ -2231,16 +2231,16 @@
         <v>0.6311932261729478</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6870578150175121</v>
+        <v>0.5598429321177905</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6870578150173086</v>
+        <v>0.5598429321176202</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.654207095554989</v>
+        <v>0.6321265897359967</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6542070955548853</v>
+        <v>0.6321265897358932</v>
       </c>
       <c r="AA6" t="n">
         <v>0.08042428114042539</v>
@@ -2249,16 +2249,16 @@
         <v>0.08042428114041549</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.08452505654871176</v>
+        <v>0.07438478261364855</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.08452505654869683</v>
+        <v>0.07438478261363513</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.08294286915735413</v>
+        <v>0.07857791752772143</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.08294286915734421</v>
+        <v>0.0785779175277115</v>
       </c>
       <c r="AG6" t="n">
         <v>0.02122330093920573</v>
@@ -2267,16 +2267,16 @@
         <v>0.02122330093920498</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.02160571434896729</v>
+        <v>0.0207134366026264</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.02160571434896615</v>
+        <v>0.02071343660262539</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0214859935243623</v>
+        <v>0.02103072238832717</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.02148599352436154</v>
+        <v>0.02103072238832642</v>
       </c>
     </row>
     <row r="7">
@@ -2295,16 +2295,16 @@
         <v>2.345789062664475</v>
       </c>
       <c r="E7" t="n">
-        <v>2.326634843410275</v>
+        <v>2.071947412424917</v>
       </c>
       <c r="F7" t="n">
-        <v>2.326634843410293</v>
+        <v>2.071947412424934</v>
       </c>
       <c r="G7" t="n">
-        <v>2.364219089796838</v>
+        <v>2.121079098468283</v>
       </c>
       <c r="H7" t="n">
-        <v>2.364219089796859</v>
+        <v>2.121079098468305</v>
       </c>
       <c r="I7" t="n">
         <v>684.9000076075548</v>
@@ -2313,16 +2313,16 @@
         <v>684.9000076076422</v>
       </c>
       <c r="K7" t="n">
-        <v>545.5513858679183</v>
+        <v>481.8056777340985</v>
       </c>
       <c r="L7" t="n">
-        <v>545.5513858679952</v>
+        <v>481.8056777341681</v>
       </c>
       <c r="M7" t="n">
-        <v>696.0684395494019</v>
+        <v>676.7124889622731</v>
       </c>
       <c r="N7" t="n">
-        <v>696.0684395494893</v>
+        <v>676.7124889623606</v>
       </c>
       <c r="O7" t="n">
         <v>0.221607022140527</v>
@@ -2331,16 +2331,16 @@
         <v>0.221607022140528</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2230321082553326</v>
+        <v>0.1986229290349186</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2230321082553341</v>
+        <v>0.19862292903492</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2262018639746813</v>
+        <v>0.2027665652072508</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2262018639746831</v>
+        <v>0.2027665652072525</v>
       </c>
       <c r="U7" t="n">
         <v>3.321360497065732</v>
@@ -2349,16 +2349,16 @@
         <v>3.321360497066309</v>
       </c>
       <c r="W7" t="n">
-        <v>1.933417175668302</v>
+        <v>1.584143183482575</v>
       </c>
       <c r="X7" t="n">
-        <v>1.933417175668724</v>
+        <v>1.584143183482928</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.33861987740645</v>
+        <v>3.316159485663455</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.338619877407011</v>
+        <v>3.316159485664016</v>
       </c>
       <c r="AA7" t="n">
         <v>0.164362997395289</v>
@@ -2367,16 +2367,16 @@
         <v>0.16436299739531</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1309219740376826</v>
+        <v>0.1156242144471128</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1309219740377011</v>
+        <v>0.1156242144471294</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1670432090024979</v>
+        <v>0.1623981483796362</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1670432090025189</v>
+        <v>0.1623981483796571</v>
       </c>
       <c r="AG7" t="n">
         <v>0.0246764636409912</v>
@@ -2385,16 +2385,16 @@
         <v>0.02467646364099493</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.01900975023441424</v>
+        <v>0.01678344606828071</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0190097502344175</v>
+        <v>0.01678344606828364</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.02495601381399763</v>
+        <v>0.02447152688122943</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02495601381400136</v>
+        <v>0.02447152688123316</v>
       </c>
     </row>
     <row r="8">
@@ -2413,16 +2413,16 @@
         <v>1.249383207595792</v>
       </c>
       <c r="E8" t="n">
-        <v>1.330834349253788</v>
+        <v>1.285937644182304</v>
       </c>
       <c r="F8" t="n">
-        <v>1.330834349253747</v>
+        <v>1.285937644182261</v>
       </c>
       <c r="G8" t="n">
-        <v>1.275356016977138</v>
+        <v>1.190261596977217</v>
       </c>
       <c r="H8" t="n">
-        <v>1.275356016977111</v>
+        <v>1.190261596977191</v>
       </c>
       <c r="I8" t="n">
         <v>335.810093249882</v>
@@ -2431,16 +2431,16 @@
         <v>335.8100932498548</v>
       </c>
       <c r="K8" t="n">
-        <v>311.0621292957319</v>
+        <v>282.68250939201</v>
       </c>
       <c r="L8" t="n">
-        <v>311.0621292957119</v>
+        <v>282.6825093919913</v>
       </c>
       <c r="M8" t="n">
-        <v>344.1312513343726</v>
+        <v>331.580682406171</v>
       </c>
       <c r="N8" t="n">
-        <v>344.1312513343452</v>
+        <v>331.5806824061436</v>
       </c>
       <c r="O8" t="n">
         <v>0.01699799872647352</v>
@@ -2449,16 +2449,16 @@
         <v>0.01699799872647318</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01823111359486897</v>
+        <v>0.01759413394044056</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01823111359486838</v>
+        <v>0.01759413394043993</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01735296899159457</v>
+        <v>0.01621334542370609</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01735296899159417</v>
+        <v>0.01621334542370569</v>
       </c>
       <c r="U8" t="n">
         <v>0.7187596353001016</v>
@@ -2467,16 +2467,16 @@
         <v>0.7187596353000264</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6194959036029026</v>
+        <v>0.5405496661382361</v>
       </c>
       <c r="X8" t="n">
-        <v>0.619495903602856</v>
+        <v>0.5405496661381944</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.7606117009603559</v>
+        <v>0.7410566694634522</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.7606117009602785</v>
+        <v>0.741056669463375</v>
       </c>
       <c r="AA8" t="n">
         <v>0.08058804623896061</v>
@@ -2485,16 +2485,16 @@
         <v>0.08058804623895412</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.07464900478801434</v>
+        <v>0.06783843486466355</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.07464900478800951</v>
+        <v>0.06783843486465906</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.08258496618256586</v>
+        <v>0.07957306794173914</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.08258496618255931</v>
+        <v>0.07957306794173261</v>
       </c>
       <c r="AG8" t="n">
         <v>0.03448261318492422</v>
@@ -2503,16 +2503,16 @@
         <v>0.03448261318492375</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.03405086998095042</v>
+        <v>0.03357510277528419</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.03405086998095008</v>
+        <v>0.03357510277528386</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.03461805105779184</v>
+        <v>0.03441377391972349</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.03461805105779137</v>
+        <v>0.03441377391972301</v>
       </c>
     </row>
     <row r="9">
@@ -2531,16 +2531,16 @@
         <v>1.215414648670439</v>
       </c>
       <c r="E9" t="n">
-        <v>1.223054896426163</v>
+        <v>1.131620308696923</v>
       </c>
       <c r="F9" t="n">
-        <v>1.223054896426162</v>
+        <v>1.131620308696922</v>
       </c>
       <c r="G9" t="n">
-        <v>1.226052749055803</v>
+        <v>1.137365192346276</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2260527490558</v>
+        <v>1.137365192346274</v>
       </c>
       <c r="I9" t="n">
         <v>619.2711847860184</v>
@@ -2549,16 +2549,16 @@
         <v>619.2711847860041</v>
       </c>
       <c r="K9" t="n">
-        <v>588.7039188947367</v>
+        <v>539.9540813885849</v>
       </c>
       <c r="L9" t="n">
-        <v>588.703918894731</v>
+        <v>539.9540813885785</v>
       </c>
       <c r="M9" t="n">
-        <v>628.1816489497982</v>
+        <v>614.7422462207206</v>
       </c>
       <c r="N9" t="n">
-        <v>628.1816489497837</v>
+        <v>614.7422462207062</v>
       </c>
       <c r="O9" t="n">
         <v>0.01866143787839252</v>
@@ -2567,16 +2567,16 @@
         <v>0.01866143787839243</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0184573314322144</v>
+        <v>0.01706704727490487</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01845733143221435</v>
+        <v>0.01706704727490482</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01869715964258556</v>
+        <v>0.01752663796685309</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01869715964258546</v>
+        <v>0.01752663796685298</v>
       </c>
       <c r="U9" t="n">
         <v>4.181440045729932</v>
@@ -2585,16 +2585,16 @@
         <v>4.181440045729329</v>
       </c>
       <c r="W9" t="n">
-        <v>2.67209363004907</v>
+        <v>2.073439946115551</v>
       </c>
       <c r="X9" t="n">
-        <v>2.67209363004893</v>
+        <v>2.073439946115476</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.691747614455234</v>
+        <v>3.699929336540223</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.691747614454787</v>
+        <v>3.699929336539737</v>
       </c>
       <c r="AA9" t="n">
         <v>0.1486133260350092</v>
@@ -2603,16 +2603,16 @@
         <v>0.1486133260350058</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1412777626122261</v>
+        <v>0.1295787272405758</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.1412777626122248</v>
+        <v>0.1295787272405743</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.1507516682482879</v>
+        <v>0.1475264667718422</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1507516682482845</v>
+        <v>0.1475264667718388</v>
       </c>
       <c r="AG9" t="n">
         <v>0.01025643025501734</v>
@@ -2621,16 +2621,16 @@
         <v>0.01025643025501708</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.009743673102224338</v>
+        <v>0.008937281821626784</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.009743673102224211</v>
+        <v>0.008937281821626652</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.01040145986512111</v>
+        <v>0.01018271577929127</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01040145986512083</v>
+        <v>0.01018271577929099</v>
       </c>
     </row>
     <row r="10">
@@ -2649,16 +2649,16 @@
         <v>2.297353639816358</v>
       </c>
       <c r="E10" t="n">
-        <v>2.330768148027796</v>
+        <v>2.213405562270665</v>
       </c>
       <c r="F10" t="n">
-        <v>2.330768148027794</v>
+        <v>2.213405562270667</v>
       </c>
       <c r="G10" t="n">
-        <v>2.34524550840041</v>
+        <v>2.187064700710589</v>
       </c>
       <c r="H10" t="n">
-        <v>2.345245508400351</v>
+        <v>2.187064700710529</v>
       </c>
       <c r="I10" t="n">
         <v>335.1276846846326</v>
@@ -2667,16 +2667,16 @@
         <v>335.1276846845912</v>
       </c>
       <c r="K10" t="n">
-        <v>347.1788696692248</v>
+        <v>317.4463891032194</v>
       </c>
       <c r="L10" t="n">
-        <v>347.1788696691634</v>
+        <v>317.4463891031622</v>
       </c>
       <c r="M10" t="n">
-        <v>343.2247875537197</v>
+        <v>331.0121548113337</v>
       </c>
       <c r="N10" t="n">
-        <v>343.2247875536784</v>
+        <v>331.0121548112924</v>
       </c>
       <c r="O10" t="n">
         <v>0.2051001262109007</v>
@@ -2685,16 +2685,16 @@
         <v>0.2051001262108993</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.208787917271418</v>
+        <v>0.1960766635195067</v>
       </c>
       <c r="R10" t="n">
-        <v>0.208787917271417</v>
+        <v>0.1960766635195058</v>
       </c>
       <c r="S10" t="n">
-        <v>0.208297109169757</v>
+        <v>0.1931321432857986</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2082971091697554</v>
+        <v>0.193132143285797</v>
       </c>
       <c r="U10" t="n">
         <v>0.6311932261730516</v>
@@ -2703,16 +2703,16 @@
         <v>0.6311932261729478</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6824438981058287</v>
+        <v>0.5896249854483625</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6824438981056268</v>
+        <v>0.5896249854481824</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.6616343670093586</v>
+        <v>0.6468534092559117</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.6616343670092529</v>
+        <v>0.646853409255806</v>
       </c>
       <c r="AA10" t="n">
         <v>0.08042428114042539</v>
@@ -2721,16 +2721,16 @@
         <v>0.08042428114041549</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.08331633671675945</v>
+        <v>0.07618110592168842</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.08331633671674472</v>
+        <v>0.07618110592167469</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.08236743208654677</v>
+        <v>0.07943663211380596</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.08236743208653685</v>
+        <v>0.07943663211379604</v>
       </c>
       <c r="AG10" t="n">
         <v>0.02122330093920573</v>
@@ -2739,16 +2739,16 @@
         <v>0.02122330093920498</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.02149777619414207</v>
+        <v>0.02087394874750405</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.02149777619414095</v>
+        <v>0.02087394874750301</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.02142597455710395</v>
+        <v>0.021120287634018</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.0214259745571032</v>
+        <v>0.02112028763401725</v>
       </c>
     </row>
     <row r="11">
@@ -2767,16 +2767,16 @@
         <v>2.345789062664475</v>
       </c>
       <c r="E11" t="n">
-        <v>2.315449698734272</v>
+        <v>2.142185239847604</v>
       </c>
       <c r="F11" t="n">
-        <v>2.31544969873429</v>
+        <v>2.142185239847621</v>
       </c>
       <c r="G11" t="n">
-        <v>2.354717979161579</v>
+        <v>2.189800635749683</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3547179791616</v>
+        <v>2.189800635749704</v>
       </c>
       <c r="I11" t="n">
         <v>684.9000076075548</v>
@@ -2785,16 +2785,16 @@
         <v>684.9000076076422</v>
       </c>
       <c r="K11" t="n">
-        <v>537.7603945757245</v>
+        <v>493.4343901534878</v>
       </c>
       <c r="L11" t="n">
-        <v>537.7603945758004</v>
+        <v>493.434390153559</v>
       </c>
       <c r="M11" t="n">
-        <v>693.5167202054955</v>
+        <v>680.5203747092447</v>
       </c>
       <c r="N11" t="n">
-        <v>693.5167202055829</v>
+        <v>680.5203747093321</v>
       </c>
       <c r="O11" t="n">
         <v>0.221607022140527</v>
@@ -2803,16 +2803,16 @@
         <v>0.221607022140528</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2219598116338948</v>
+        <v>0.205356007557527</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2219598116338964</v>
+        <v>0.2053560075575285</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2252715943205352</v>
+        <v>0.2093717638384253</v>
       </c>
       <c r="T11" t="n">
-        <v>0.225271594320537</v>
+        <v>0.2093717638384271</v>
       </c>
       <c r="U11" t="n">
         <v>3.321360497065732</v>
@@ -2821,16 +2821,16 @@
         <v>3.321360497066309</v>
       </c>
       <c r="W11" t="n">
-        <v>1.92047222075394</v>
+        <v>1.671158713339828</v>
       </c>
       <c r="X11" t="n">
-        <v>1.920472220754359</v>
+        <v>1.671158713340203</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.404686044279716</v>
+        <v>3.389983846628815</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.40468604428029</v>
+        <v>3.38998384662939</v>
       </c>
       <c r="AA11" t="n">
         <v>0.164362997395289</v>
@@ -2839,16 +2839,16 @@
         <v>0.16436299739531</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1290522840577705</v>
+        <v>0.1184148846294291</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.1290522840577888</v>
+        <v>0.1184148846294462</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.1664308448103277</v>
+        <v>0.1633119686572812</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1664308448103486</v>
+        <v>0.1633119686573022</v>
       </c>
       <c r="AG11" t="n">
         <v>0.0246764636409912</v>
@@ -2857,16 +2857,16 @@
         <v>0.02467646364099493</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.01873837522834318</v>
+        <v>0.01718866543504108</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.01873837522834639</v>
+        <v>0.01718866543504408</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.02489214329145989</v>
+        <v>0.02456683973489568</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.02489214329146362</v>
+        <v>0.02456683973489941</v>
       </c>
     </row>
     <row r="12">
@@ -2885,16 +2885,16 @@
         <v>1.249383207595792</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3031447463793</v>
+        <v>1.389127100225801</v>
       </c>
       <c r="F12" t="n">
-        <v>1.30314474637926</v>
+        <v>1.389127100225769</v>
       </c>
       <c r="G12" t="n">
-        <v>1.105027565371852</v>
+        <v>1.205402785030673</v>
       </c>
       <c r="H12" t="n">
-        <v>1.105027565371848</v>
+        <v>1.205402785030671</v>
       </c>
       <c r="I12" t="n">
         <v>335.810093249882</v>
@@ -2903,16 +2903,16 @@
         <v>335.8100932498548</v>
       </c>
       <c r="K12" t="n">
-        <v>269.9653435233846</v>
+        <v>293.5190039395302</v>
       </c>
       <c r="L12" t="n">
-        <v>269.9653435233672</v>
+        <v>293.5190039395108</v>
       </c>
       <c r="M12" t="n">
-        <v>321.7213915807532</v>
+        <v>337.4484388835511</v>
       </c>
       <c r="N12" t="n">
-        <v>321.7213915807258</v>
+        <v>337.4484388835237</v>
       </c>
       <c r="O12" t="n">
         <v>0.01699799872647352</v>
@@ -2921,16 +2921,16 @@
         <v>0.01699799872647318</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.01785189946258983</v>
+        <v>0.01904749307399976</v>
       </c>
       <c r="R12" t="n">
-        <v>0.01785189946258925</v>
+        <v>0.01904749307399928</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01581220239032785</v>
+        <v>0.01718937460360374</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01581220239032765</v>
+        <v>0.01718937460360357</v>
       </c>
       <c r="U12" t="n">
         <v>0.7187596353001016</v>
@@ -2939,16 +2939,16 @@
         <v>0.7187596353000264</v>
       </c>
       <c r="W12" t="n">
-        <v>0.4104921282085087</v>
+        <v>0.4555743327525296</v>
       </c>
       <c r="X12" t="n">
-        <v>0.4104921282084778</v>
+        <v>0.4555743327524924</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5835968813276599</v>
+        <v>0.6015693291544358</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.5835968813275964</v>
+        <v>0.601569329154372</v>
       </c>
       <c r="AA12" t="n">
         <v>0.08058804623896061</v>
@@ -2957,16 +2957,16 @@
         <v>0.08058804623895412</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.06478655652136821</v>
+        <v>0.07043898779984283</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.06478655652136402</v>
+        <v>0.07043898779983816</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.07720702534536339</v>
+        <v>0.08098121808321268</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.07720702534535687</v>
+        <v>0.08098121808320614</v>
       </c>
       <c r="AG12" t="n">
         <v>0.03448261318492422</v>
@@ -2975,16 +2975,16 @@
         <v>0.03448261318492375</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.03336561325339493</v>
+        <v>0.0337558290009186</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.03336561325339464</v>
+        <v>0.03375582900091827</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.03425330089856232</v>
+        <v>0.03450927943082329</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.03425330089856186</v>
+        <v>0.03450927943082282</v>
       </c>
     </row>
     <row r="13">
@@ -3003,16 +3003,16 @@
         <v>1.21541464867044</v>
       </c>
       <c r="E13" t="n">
-        <v>1.197550161296837</v>
+        <v>1.307758929089211</v>
       </c>
       <c r="F13" t="n">
-        <v>1.197550161296837</v>
+        <v>1.307758929089214</v>
       </c>
       <c r="G13" t="n">
-        <v>1.205536638909191</v>
+        <v>1.313006417407342</v>
       </c>
       <c r="H13" t="n">
-        <v>1.205536638909189</v>
+        <v>1.313006417407343</v>
       </c>
       <c r="I13" t="n">
         <v>619.2711847860421</v>
@@ -3021,16 +3021,16 @@
         <v>619.2711847860321</v>
       </c>
       <c r="K13" t="n">
-        <v>510.9781770919314</v>
+        <v>560.5029812843843</v>
       </c>
       <c r="L13" t="n">
-        <v>510.9781770919462</v>
+        <v>560.502981284406</v>
       </c>
       <c r="M13" t="n">
-        <v>604.1847184477883</v>
+        <v>621.025558385061</v>
       </c>
       <c r="N13" t="n">
-        <v>604.1847184477781</v>
+        <v>621.0255583850508</v>
       </c>
       <c r="O13" t="n">
         <v>0.01866143787839267</v>
@@ -3039,16 +3039,16 @@
         <v>0.01866143787839261</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01807317154947907</v>
+        <v>0.01976587177490398</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01807317154947915</v>
+        <v>0.01976587177490413</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01871208975846738</v>
+        <v>0.02018567084035452</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0187120897584673</v>
+        <v>0.02018567084035445</v>
       </c>
       <c r="U13" t="n">
         <v>4.181440045730522</v>
@@ -3057,16 +3057,16 @@
         <v>4.181440045730588</v>
       </c>
       <c r="W13" t="n">
-        <v>1.770690826556224</v>
+        <v>2.459402754087947</v>
       </c>
       <c r="X13" t="n">
-        <v>1.770690826556533</v>
+        <v>2.459402754088462</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.540944914621799</v>
+        <v>3.587060342554841</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.540944914621798</v>
+        <v>3.587060342554832</v>
       </c>
       <c r="AA13" t="n">
         <v>0.148613326035015</v>
@@ -3075,16 +3075,16 @@
         <v>0.1486133260350125</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.122625060384777</v>
+        <v>0.1345100730465823</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1226250603847805</v>
+        <v>0.1345100730465875</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.1449928605657265</v>
+        <v>0.1490343423878883</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.1449928605657241</v>
+        <v>0.1490343423878859</v>
       </c>
       <c r="AG13" t="n">
         <v>0.01025643025501777</v>
@@ -3093,16 +3093,16 @@
         <v>0.01025643025501761</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.008457237349983939</v>
+        <v>0.009277394725272578</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.00845723734998419</v>
+        <v>0.009277394725272944</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.01001087802668667</v>
+        <v>0.0102849850097831</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01001087802668651</v>
+        <v>0.01028498500978294</v>
       </c>
     </row>
     <row r="14">
@@ -3121,16 +3121,16 @@
         <v>1.264628069292649</v>
       </c>
       <c r="E14" t="n">
-        <v>1.215333108041731</v>
+        <v>1.323239252490129</v>
       </c>
       <c r="F14" t="n">
-        <v>1.21533255720396</v>
+        <v>1.323239252490131</v>
       </c>
       <c r="G14" t="n">
-        <v>1.254971400872743</v>
+        <v>1.363692616343134</v>
       </c>
       <c r="H14" t="n">
-        <v>1.254971400872742</v>
+        <v>1.363692616343136</v>
       </c>
       <c r="I14" t="n">
         <v>1196.201767831233</v>
@@ -3139,16 +3139,16 @@
         <v>1196.201767831233</v>
       </c>
       <c r="K14" t="n">
-        <v>718.5148461540236</v>
+        <v>735.3492575146622</v>
       </c>
       <c r="L14" t="n">
-        <v>718.5084175773893</v>
+        <v>735.349257514662</v>
       </c>
       <c r="M14" t="n">
-        <v>1181.115301492979</v>
+        <v>1197.956141430252</v>
       </c>
       <c r="N14" t="n">
-        <v>1181.115301492979</v>
+        <v>1197.956141430252</v>
       </c>
       <c r="O14" t="n">
         <v>0.02231289726475464</v>
@@ -3157,16 +3157,16 @@
         <v>0.02231289726475464</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01949580728907056</v>
+        <v>0.02100429764697745</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01949576322204896</v>
+        <v>0.02100429764697747</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02266687071555156</v>
+        <v>0.02424056675521793</v>
       </c>
       <c r="T14" t="n">
-        <v>0.02266687071555154</v>
+        <v>0.02424056675521795</v>
       </c>
       <c r="U14" t="n">
         <v>5.104851645040209</v>
@@ -3175,16 +3175,16 @@
         <v>5.104851645040209</v>
       </c>
       <c r="W14" t="n">
-        <v>1.864740983099519</v>
+        <v>1.880643144582608</v>
       </c>
       <c r="X14" t="n">
-        <v>1.864717351784814</v>
+        <v>1.880643144582608</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.633230032435653</v>
+        <v>5.898628601665106</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.633230032435653</v>
+        <v>5.898628601665106</v>
       </c>
       <c r="AA14" t="n">
         <v>0.2870657115877016</v>
@@ -3193,16 +3193,16 @@
         <v>0.2870657115877016</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.1724299203900134</v>
+        <v>0.1764698594758446</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.1724283776536827</v>
+        <v>0.1764698594758446</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.2834452461184132</v>
+        <v>0.2874867279405749</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.2834452461184131</v>
+        <v>0.2874867279405749</v>
       </c>
       <c r="AG14" t="n">
         <v>0.01959602438352584</v>
@@ -3211,16 +3211,16 @@
         <v>0.01959602438352584</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.01177128867854098</v>
+        <v>0.01204529045429602</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01177118347119959</v>
+        <v>0.01204529045429602</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.01935047215519474</v>
+        <v>0.01962457913829118</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01935047215519474</v>
+        <v>0.01962457913829117</v>
       </c>
     </row>
     <row r="15">
@@ -3239,16 +3239,16 @@
         <v>2.297353639816358</v>
       </c>
       <c r="E15" t="n">
-        <v>2.282215653974355</v>
+        <v>2.442628474549328</v>
       </c>
       <c r="F15" t="n">
-        <v>2.282215653974355</v>
+        <v>2.442628474549322</v>
       </c>
       <c r="G15" t="n">
-        <v>2.097121851084944</v>
+        <v>2.282652265800293</v>
       </c>
       <c r="H15" t="n">
-        <v>2.097121851084932</v>
+        <v>2.28265226580028</v>
       </c>
       <c r="I15" t="n">
         <v>335.1276846846326</v>
@@ -3257,16 +3257,16 @@
         <v>335.1276846845912</v>
       </c>
       <c r="K15" t="n">
-        <v>301.3107437093103</v>
+        <v>329.5372417900981</v>
       </c>
       <c r="L15" t="n">
-        <v>301.3107437092571</v>
+        <v>329.5372417900388</v>
       </c>
       <c r="M15" t="n">
-        <v>321.4183349104175</v>
+        <v>336.7219162803118</v>
       </c>
       <c r="N15" t="n">
-        <v>321.4183349103761</v>
+        <v>336.7219162802705</v>
       </c>
       <c r="O15" t="n">
         <v>0.2051001262109007</v>
@@ -3275,16 +3275,16 @@
         <v>0.2051001262108993</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.204434324390698</v>
+        <v>0.2191572841616066</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2044343243906969</v>
+        <v>0.2191572841616052</v>
       </c>
       <c r="S15" t="n">
-        <v>0.201414625622615</v>
+        <v>0.2174875202568134</v>
       </c>
       <c r="T15" t="n">
-        <v>0.201414625622614</v>
+        <v>0.2174875202568124</v>
       </c>
       <c r="U15" t="n">
         <v>0.6311932261730516</v>
@@ -3293,16 +3293,16 @@
         <v>0.6311932261729478</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4522084073817672</v>
+        <v>0.5161205092667469</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4522084073816333</v>
+        <v>0.5161205092665873</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5222816079108108</v>
+        <v>0.5375557012830664</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.5222816079107214</v>
+        <v>0.537555701282977</v>
       </c>
       <c r="AA15" t="n">
         <v>0.08042428114042539</v>
@@ -3311,16 +3311,16 @@
         <v>0.08042428114041549</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.07230885740016404</v>
+        <v>0.07908268099338701</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.07230885740015125</v>
+        <v>0.07908268099337278</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0771342974987234</v>
+        <v>0.08080686645316824</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.07713429749871348</v>
+        <v>0.08080686645315834</v>
       </c>
       <c r="AG15" t="n">
         <v>0.02122330093920573</v>
@@ -3329,16 +3329,16 @@
         <v>0.02122330093920498</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.02051501960759695</v>
+        <v>0.02113273965021969</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.02051501960759598</v>
+        <v>0.02113273965021861</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.02088015060967489</v>
+        <v>0.02126320517291597</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.02088015060967414</v>
+        <v>0.02126320517291522</v>
       </c>
     </row>
     <row r="16">
@@ -3357,16 +3357,16 @@
         <v>1.249383207595792</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3031447463793</v>
+        <v>1.389127100225802</v>
       </c>
       <c r="F16" t="n">
-        <v>1.30314474637926</v>
+        <v>1.389127100225769</v>
       </c>
       <c r="G16" t="n">
-        <v>1.105027565371852</v>
+        <v>1.205402785030673</v>
       </c>
       <c r="H16" t="n">
-        <v>1.105027565371848</v>
+        <v>1.205402785030671</v>
       </c>
       <c r="I16" t="n">
         <v>335.810093249882</v>
@@ -3375,16 +3375,16 @@
         <v>335.8100932498548</v>
       </c>
       <c r="K16" t="n">
-        <v>269.9653435233847</v>
+        <v>293.5190039395302</v>
       </c>
       <c r="L16" t="n">
-        <v>269.9653435233672</v>
+        <v>293.5190039395108</v>
       </c>
       <c r="M16" t="n">
-        <v>321.7213915807532</v>
+        <v>337.4484388835511</v>
       </c>
       <c r="N16" t="n">
-        <v>321.7213915807258</v>
+        <v>337.4484388835237</v>
       </c>
       <c r="O16" t="n">
         <v>0.01699799872647352</v>
@@ -3393,16 +3393,16 @@
         <v>0.01699799872647318</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01785189946258983</v>
+        <v>0.01904749307399976</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01785189946258925</v>
+        <v>0.01904749307399928</v>
       </c>
       <c r="S16" t="n">
-        <v>0.01581220239032785</v>
+        <v>0.01718937460360375</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01581220239032765</v>
+        <v>0.01718937460360357</v>
       </c>
       <c r="U16" t="n">
         <v>0.7187596353001016</v>
@@ -3411,16 +3411,16 @@
         <v>0.7187596353000264</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4104921282085087</v>
+        <v>0.4555743327525296</v>
       </c>
       <c r="X16" t="n">
-        <v>0.4104921282084778</v>
+        <v>0.4555743327524924</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5835968813276599</v>
+        <v>0.6015693291544358</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.5835968813275964</v>
+        <v>0.601569329154372</v>
       </c>
       <c r="AA16" t="n">
         <v>0.08058804623896061</v>
@@ -3429,16 +3429,16 @@
         <v>0.08058804623895412</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.06478655652136821</v>
+        <v>0.07043898779984283</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.06478655652136402</v>
+        <v>0.07043898779983816</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.07720702534536339</v>
+        <v>0.08098121808321268</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.07720702534535687</v>
+        <v>0.08098121808320614</v>
       </c>
       <c r="AG16" t="n">
         <v>0.03448261318492422</v>
@@ -3447,16 +3447,16 @@
         <v>0.03448261318492375</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.03336561325339493</v>
+        <v>0.0337558290009186</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.03336561325339464</v>
+        <v>0.03375582900091827</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.03425330089856232</v>
+        <v>0.03450927943082329</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.03425330089856186</v>
+        <v>0.03450927943082282</v>
       </c>
     </row>
     <row r="17">
@@ -3709,16 +3709,16 @@
         <v>21.81223996439638</v>
       </c>
       <c r="E19" t="n">
-        <v>22.05655953962632</v>
+        <v>21.54564267489084</v>
       </c>
       <c r="F19" t="n">
-        <v>22.05655898878842</v>
+        <v>21.54564267489072</v>
       </c>
       <c r="G19" t="n">
-        <v>21.53183246107693</v>
+        <v>20.90758338800455</v>
       </c>
       <c r="H19" t="n">
-        <v>21.53183246107677</v>
+        <v>20.9075833880044</v>
       </c>
       <c r="I19" t="n">
         <v>6844.965817391977</v>
@@ -3727,16 +3727,16 @@
         <v>6844.965817391885</v>
       </c>
       <c r="K19" t="n">
-        <v>5738.54009032065</v>
+        <v>5513.466986269082</v>
       </c>
       <c r="L19" t="n">
-        <v>5738.533661743943</v>
+        <v>5513.46698626901</v>
       </c>
       <c r="M19" t="n">
-        <v>6850.849475312064</v>
+        <v>6803.837342074753</v>
       </c>
       <c r="N19" t="n">
-        <v>6850.84947531197</v>
+        <v>6803.837342074659</v>
       </c>
       <c r="O19" t="n">
         <v>1.45634482127692</v>
@@ -3745,16 +3745,16 @@
         <v>1.456344821276916</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.466378563974153</v>
+        <v>1.409206313085661</v>
       </c>
       <c r="R19" t="n">
-        <v>1.466378519907129</v>
+        <v>1.409206313085659</v>
       </c>
       <c r="S19" t="n">
-        <v>1.467618076002954</v>
+        <v>1.407030001059383</v>
       </c>
       <c r="T19" t="n">
-        <v>1.467618076002951</v>
+        <v>1.40703000105938</v>
       </c>
       <c r="U19" t="n">
         <v>29.19735483604114</v>
@@ -3763,16 +3763,16 @@
         <v>29.19735483604121</v>
       </c>
       <c r="W19" t="n">
-        <v>16.87426788634922</v>
+        <v>15.31064297240067</v>
       </c>
       <c r="X19" t="n">
-        <v>16.8742442550353</v>
+        <v>15.31064297240135</v>
       </c>
       <c r="Y19" t="n">
-        <v>27.74544823479723</v>
+        <v>27.99025108737341</v>
       </c>
       <c r="Z19" t="n">
-        <v>27.74544823479732</v>
+        <v>27.99025108737341</v>
       </c>
       <c r="AA19" t="n">
         <v>1.642661828468681</v>
@@ -3781,16 +3781,16 @@
         <v>1.642661828468659</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.377140662054988</v>
+        <v>1.323127390622562</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.37713911931864</v>
+        <v>1.323127390622545</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.644073794654478</v>
+        <v>1.632791775312965</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.644073794654455</v>
+        <v>1.632791775312942</v>
       </c>
       <c r="AG19" t="n">
         <v>0.3056420782375127</v>
@@ -3799,16 +3799,16 @@
         <v>0.3056420782375154</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.2804553351872513</v>
+        <v>0.2745527999750175</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.2804552299799123</v>
+        <v>0.2745527999750196</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.3059537864072475</v>
+        <v>0.3047732206655252</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.3059537864072503</v>
+        <v>0.3047732206655279</v>
       </c>
     </row>
   </sheetData>
@@ -4444,55 +4444,55 @@
         <v>4.965394307439629</v>
       </c>
       <c r="C4" t="n">
-        <v>5.111475925128247</v>
+        <v>4.731712388313895</v>
       </c>
       <c r="D4" t="n">
-        <v>5.081602833500321</v>
+        <v>4.59490203156613</v>
       </c>
       <c r="E4" t="n">
         <v>1332.14616699511</v>
       </c>
       <c r="F4" t="n">
-        <v>1306.959089355727</v>
+        <v>1155.126601369923</v>
       </c>
       <c r="G4" t="n">
-        <v>1364.975641047032</v>
+        <v>1308.07905244273</v>
       </c>
       <c r="H4" t="n">
         <v>0.3996213971670763</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4055238214259688</v>
+        <v>0.3837877338208479</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4047000308204823</v>
+        <v>0.3790476800717276</v>
       </c>
       <c r="K4" t="n">
         <v>5.615955500930178</v>
       </c>
       <c r="L4" t="n">
-        <v>4.085439338482216</v>
+        <v>3.032130158201323</v>
       </c>
       <c r="M4" t="n">
-        <v>4.972217066830099</v>
+        <v>4.917603789777237</v>
       </c>
       <c r="N4" t="n">
         <v>0.3196897861642632</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3136453657664626</v>
+        <v>0.2772084515452112</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3275682365922803</v>
+        <v>0.3139141356422215</v>
       </c>
       <c r="Q4" t="n">
         <v>0.06860473460007309</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06825902827555319</v>
+        <v>0.06554618226694309</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06923095120438001</v>
+        <v>0.06814565850501833</v>
       </c>
     </row>
     <row r="5">
@@ -4505,55 +4505,55 @@
         <v>2.46274232523871</v>
       </c>
       <c r="C5" t="n">
-        <v>2.443588105984536</v>
+        <v>2.188900674999177</v>
       </c>
       <c r="D5" t="n">
-        <v>2.481172352371098</v>
+        <v>2.238032361042544</v>
       </c>
       <c r="E5" t="n">
         <v>715.4898562671077</v>
       </c>
       <c r="F5" t="n">
-        <v>576.1412345274712</v>
+        <v>512.3955263936514</v>
       </c>
       <c r="G5" t="n">
-        <v>726.6582882089548</v>
+        <v>707.302337621826</v>
       </c>
       <c r="H5" t="n">
         <v>0.314286380346555</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3157114664613606</v>
+        <v>0.2913022872409466</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3188812221807093</v>
+        <v>0.2954459234132787</v>
       </c>
       <c r="K5" t="n">
         <v>3.373641743298164</v>
       </c>
       <c r="L5" t="n">
-        <v>1.985698421900734</v>
+        <v>1.636424429715007</v>
       </c>
       <c r="M5" t="n">
-        <v>3.390901123638882</v>
+        <v>3.368440731895887</v>
       </c>
       <c r="N5" t="n">
         <v>0.1717039802536704</v>
       </c>
       <c r="O5" t="n">
-        <v>0.138262956896064</v>
+        <v>0.1229651973054942</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1743841918608794</v>
+        <v>0.1697391312380176</v>
       </c>
       <c r="Q5" t="n">
         <v>0.02635755366970334</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02069084026312638</v>
+        <v>0.01846453609699285</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02663710384270977</v>
+        <v>0.02615261690994157</v>
       </c>
     </row>
     <row r="6">
@@ -4566,55 +4566,55 @@
         <v>2.464797856266255</v>
       </c>
       <c r="C6" t="n">
-        <v>2.553889245679951</v>
+        <v>2.417557952879227</v>
       </c>
       <c r="D6" t="n">
-        <v>2.501408766032941</v>
+        <v>2.327626789323493</v>
       </c>
       <c r="E6" t="n">
         <v>955.0812780359004</v>
       </c>
       <c r="F6" t="n">
-        <v>899.7660481904686</v>
+        <v>822.6365907805948</v>
       </c>
       <c r="G6" t="n">
-        <v>972.3129002841708</v>
+        <v>946.3229286268916</v>
       </c>
       <c r="H6" t="n">
         <v>0.03565943660486603</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03668844502708337</v>
+        <v>0.03466118121534543</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03605012863418014</v>
+        <v>0.03373998339055918</v>
       </c>
       <c r="K6" t="n">
         <v>4.900199681030034</v>
       </c>
       <c r="L6" t="n">
-        <v>3.291589533651972</v>
+        <v>2.613989612253787</v>
       </c>
       <c r="M6" t="n">
-        <v>4.45235931541559</v>
+        <v>4.440986006003675</v>
       </c>
       <c r="N6" t="n">
         <v>0.2292013722739699</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2159267674002405</v>
+        <v>0.1974171621052394</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2333366344308538</v>
+        <v>0.2270995347135813</v>
       </c>
       <c r="Q6" t="n">
         <v>0.04473904343994156</v>
       </c>
       <c r="R6" t="n">
-        <v>0.04379454308317476</v>
+        <v>0.04251238459691097</v>
       </c>
       <c r="S6" t="n">
-        <v>0.04501951092291295</v>
+        <v>0.04459648969901475</v>
       </c>
     </row>
     <row r="7">
@@ -4627,55 +4627,55 @@
         <v>4.64314270248086</v>
       </c>
       <c r="C7" t="n">
-        <v>4.646217846762069</v>
+        <v>4.35559080211827</v>
       </c>
       <c r="D7" t="n">
-        <v>4.699963487561989</v>
+        <v>4.376865336460272</v>
       </c>
       <c r="E7" t="n">
         <v>1020.027692292187</v>
       </c>
       <c r="F7" t="n">
-        <v>884.9392642449493</v>
+        <v>810.8807792567072</v>
       </c>
       <c r="G7" t="n">
-        <v>1036.741507759215</v>
+        <v>1011.532529520578</v>
       </c>
       <c r="H7" t="n">
         <v>0.4267071483514276</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4307477289053129</v>
+        <v>0.4014326710770337</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4335687034902922</v>
+        <v>0.402503907124224</v>
       </c>
       <c r="K7" t="n">
         <v>3.952553723238783</v>
       </c>
       <c r="L7" t="n">
-        <v>2.602916118859769</v>
+        <v>2.260783698788191</v>
       </c>
       <c r="M7" t="n">
-        <v>4.066320411289074</v>
+        <v>4.036837255884727</v>
       </c>
       <c r="N7" t="n">
         <v>0.2447872785357144</v>
       </c>
       <c r="O7" t="n">
-        <v>0.21236862077453</v>
+        <v>0.1945959905511175</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2487982768968744</v>
+        <v>0.2427486007710872</v>
       </c>
       <c r="Q7" t="n">
         <v>0.04589976458019693</v>
       </c>
       <c r="R7" t="n">
-        <v>0.04023615142248524</v>
+        <v>0.03806261418254513</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04631811784856384</v>
+        <v>0.04568712736891368</v>
       </c>
     </row>
     <row r="8">
@@ -4688,55 +4688,55 @@
         <v>2.464797856266256</v>
       </c>
       <c r="C8" t="n">
-        <v>2.500694907676137</v>
+        <v>2.696886029315012</v>
       </c>
       <c r="D8" t="n">
-        <v>2.310564204281043</v>
+        <v>2.518409202438015</v>
       </c>
       <c r="E8" t="n">
         <v>955.0812780359241</v>
       </c>
       <c r="F8" t="n">
-        <v>780.9435206153159</v>
+        <v>854.0219852239145</v>
       </c>
       <c r="G8" t="n">
-        <v>925.9061100285414</v>
+        <v>958.473997268612</v>
       </c>
       <c r="H8" t="n">
         <v>0.03565943660486619</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03592507101206889</v>
+        <v>0.03881336484890374</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03452429214879524</v>
+        <v>0.03737504544395827</v>
       </c>
       <c r="K8" t="n">
         <v>4.900199681030624</v>
       </c>
       <c r="L8" t="n">
-        <v>2.181182954764733</v>
+        <v>2.914977086840477</v>
       </c>
       <c r="M8" t="n">
-        <v>4.124541795949459</v>
+        <v>4.188629671709276</v>
       </c>
       <c r="N8" t="n">
         <v>0.2292013722739756</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1874116169061452</v>
+        <v>0.2049490608464251</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2221998859110899</v>
+        <v>0.230015560471101</v>
       </c>
       <c r="Q8" t="n">
         <v>0.04473904343994198</v>
       </c>
       <c r="R8" t="n">
-        <v>0.04182285060337886</v>
+        <v>0.04303322372619118</v>
       </c>
       <c r="S8" t="n">
-        <v>0.04426417892524899</v>
+        <v>0.0447942644406064</v>
       </c>
     </row>
     <row r="9">
@@ -4749,55 +4749,55 @@
         <v>4.811364916704875</v>
       </c>
       <c r="C9" t="n">
-        <v>4.800693508395386</v>
+        <v>5.154994827265259</v>
       </c>
       <c r="D9" t="n">
-        <v>4.457120817329539</v>
+        <v>4.8517476671741</v>
       </c>
       <c r="E9" t="n">
         <v>1867.139545765748</v>
       </c>
       <c r="F9" t="n">
-        <v>1289.790933386719</v>
+        <v>1358.40550324429</v>
       </c>
       <c r="G9" t="n">
-        <v>1824.25502798415</v>
+        <v>1872.126496594115</v>
       </c>
       <c r="H9" t="n">
         <v>0.2444110222021288</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2417820311423584</v>
+        <v>0.2592090748825838</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2398936987284944</v>
+        <v>0.2589174616156351</v>
       </c>
       <c r="K9" t="n">
         <v>6.454804506513362</v>
       </c>
       <c r="L9" t="n">
-        <v>2.727441518689794</v>
+        <v>2.852337986601885</v>
       </c>
       <c r="M9" t="n">
-        <v>6.739108521674124</v>
+        <v>7.037753632102608</v>
       </c>
       <c r="N9" t="n">
         <v>0.4480780389670875</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3095253343115457</v>
+        <v>0.3259915282690745</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4377865689625</v>
+        <v>0.4492748124769559</v>
       </c>
       <c r="Q9" t="n">
         <v>0.07530193850765579</v>
       </c>
       <c r="R9" t="n">
-        <v>0.06565192153953285</v>
+        <v>0.06693385910543431</v>
       </c>
       <c r="S9" t="n">
-        <v>0.07448392366343196</v>
+        <v>0.07539706374203045</v>
       </c>
     </row>
   </sheetData>
